--- a/DataAnalysis/CS/0.05/Results.xlsx
+++ b/DataAnalysis/CS/0.05/Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CS\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877620BE-3C75-4D62-AF63-91879E0941BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75A3C30-12B2-4C51-B5F4-CBC774516468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -4586,23 +4586,23 @@
         <v>69</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R34" si="0">AVERAGE(C3:D3)</f>
+        <f t="shared" ref="R3:R11" si="0">AVERAGE(C3:D3)</f>
         <v>20.5</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S34" si="1">AVERAGE(H3,I3)</f>
+        <f t="shared" ref="S3:S11" si="1">AVERAGE(H3,I3)</f>
         <v>15</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T34" si="2">AVERAGE(M3:N3)</f>
+        <f t="shared" ref="T3:T11" si="2">AVERAGE(M3:N3)</f>
         <v>23</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U34" si="3">AVERAGE(R3:T3)</f>
+        <f t="shared" ref="U3:U11" si="3">AVERAGE(R3:T3)</f>
         <v>19.5</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD34" si="4">MIN(R3:T3)</f>
+        <f t="shared" ref="AD3:AD11" si="4">MIN(R3:T3)</f>
         <v>15</v>
       </c>
       <c r="AE3">
@@ -10863,7 +10863,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF13"/>
+  <dimension ref="A2:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11591,6 +11591,170 @@
       <c r="AD13">
         <f t="shared" si="5"/>
         <v>1.8333333333333321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>93</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>62</v>
+      </c>
+      <c r="G15">
+        <v>86</v>
+      </c>
+      <c r="H15">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>15</v>
+      </c>
+      <c r="J15">
+        <v>85</v>
+      </c>
+      <c r="L15">
+        <v>72</v>
+      </c>
+      <c r="M15">
+        <v>28</v>
+      </c>
+      <c r="N15">
+        <v>17</v>
+      </c>
+      <c r="O15">
+        <v>83</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" ref="Q14:Q16" si="6">AVERAGE(C15:D15)</f>
+        <v>22.5</v>
+      </c>
+      <c r="R15">
+        <f t="shared" ref="R14:R16" si="7">AVERAGE(H15:I15)</f>
+        <v>14.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" ref="S14:S16" si="8">AVERAGE(M15:N15)</f>
+        <v>22.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" ref="T14:T16" si="9">AVERAGE(Q15:S15)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U15">
+        <f>AVERAGE(Q15:Q24)</f>
+        <v>25</v>
+      </c>
+      <c r="V15">
+        <f>_xlfn.STDEV.S(Q15:Q24)</f>
+        <v>3.5355339059327378</v>
+      </c>
+      <c r="W15">
+        <f>AVERAGE(R15:R24)</f>
+        <v>17.5</v>
+      </c>
+      <c r="X15">
+        <f>_xlfn.STDEV.S(R15:R24)</f>
+        <v>4.2426406871192848</v>
+      </c>
+      <c r="Y15">
+        <f>AVERAGE(S15:S24)</f>
+        <v>21.25</v>
+      </c>
+      <c r="Z15">
+        <f>_xlfn.STDEV.S(S15:S24)</f>
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="AA15">
+        <f>AVERAGE(T15:T24)</f>
+        <v>21.25</v>
+      </c>
+      <c r="AB15">
+        <f>_xlfn.STDEV.S(T15:T24)</f>
+        <v>2.0034692133618863</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" ref="AC14:AC16" si="10">MIN(Q15:S15)</f>
+        <v>14.5</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" ref="AD14:AD16" si="11">T15-AC15</f>
+        <v>5.3333333333333321</v>
+      </c>
+      <c r="AE15">
+        <f>AVERAGE(AD15:AD24)</f>
+        <v>4</v>
+      </c>
+      <c r="AF15">
+        <f>_xlfn.STDEV.S(AD15:AD24)</f>
+        <v>1.8856180831641252</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>91</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>46</v>
+      </c>
+      <c r="E16">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>83</v>
+      </c>
+      <c r="H16">
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>24</v>
+      </c>
+      <c r="J16">
+        <v>76</v>
+      </c>
+      <c r="L16">
+        <v>81</v>
+      </c>
+      <c r="M16">
+        <v>19</v>
+      </c>
+      <c r="N16">
+        <v>21</v>
+      </c>
+      <c r="O16">
+        <v>79</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>27.5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="7"/>
+        <v>20.5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="9"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="11"/>
+        <v>2.6666666666666679</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/CS/0.05/Results.xlsx
+++ b/DataAnalysis/CS/0.05/Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CS\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75A3C30-12B2-4C51-B5F4-CBC774516468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD82391-C29B-4B0B-9392-4B45BAA42556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="73">
   <si>
     <t>Dati originali</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>ep=0.1</t>
+  </si>
+  <si>
+    <t>try3</t>
   </si>
 </sst>
 </file>
@@ -585,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -821,366 +824,401 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9">
+        <v>22.166666666666668</v>
+      </c>
+      <c r="H9">
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="I9">
+        <v>20.5</v>
+      </c>
+      <c r="J9">
+        <v>5.0744457825461096</v>
+      </c>
+      <c r="K9">
+        <v>24.5</v>
+      </c>
+      <c r="L9">
+        <v>3.0413812651491097</v>
+      </c>
+      <c r="M9">
+        <v>22.388888888888886</v>
+      </c>
+      <c r="N9">
+        <v>2.1235016504018209</v>
+      </c>
+      <c r="O9">
+        <v>3.0555555555555549</v>
+      </c>
+      <c r="P9">
+        <v>2.0161385901804505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10">
-        <v>23.45</v>
-      </c>
-      <c r="H10">
-        <v>2.6399705385561569</v>
-      </c>
-      <c r="I10">
-        <v>20.2</v>
-      </c>
-      <c r="J10">
-        <v>2.8205594401741556</v>
-      </c>
-      <c r="K10">
-        <v>25.95</v>
-      </c>
-      <c r="L10">
-        <v>1.6236105170610073</v>
-      </c>
-      <c r="M10">
-        <v>23.2</v>
-      </c>
-      <c r="N10">
-        <v>1.6059303676308667</v>
-      </c>
-      <c r="O10">
-        <v>3.0999999999999996</v>
-      </c>
-      <c r="P10">
-        <v>1.8260799273949007</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>23.45</v>
+      </c>
+      <c r="H11">
+        <v>2.6399705385561569</v>
+      </c>
+      <c r="I11">
+        <v>20.2</v>
+      </c>
+      <c r="J11">
+        <v>2.8205594401741556</v>
+      </c>
+      <c r="K11">
+        <v>25.95</v>
+      </c>
+      <c r="L11">
+        <v>1.6236105170610073</v>
+      </c>
+      <c r="M11">
+        <v>23.2</v>
+      </c>
+      <c r="N11">
+        <v>1.6059303676308667</v>
+      </c>
+      <c r="O11">
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="P11">
+        <v>1.8260799273949007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
         <v>2</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>21</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>23.625</v>
       </c>
-      <c r="H11">
+      <c r="H12">
         <v>3.0325613879076827</v>
       </c>
-      <c r="I11">
+      <c r="I12">
         <v>19.75</v>
       </c>
-      <c r="J11">
+      <c r="J12">
         <v>3.1847852585154217</v>
       </c>
-      <c r="K11">
+      <c r="K12">
         <v>21.9375</v>
       </c>
-      <c r="L11">
+      <c r="L12">
         <v>1.9353386562267894</v>
       </c>
-      <c r="M11">
+      <c r="M12">
         <v>21.770833333333332</v>
       </c>
-      <c r="N11">
+      <c r="N12">
         <v>1.1301689015504479</v>
       </c>
-      <c r="O11">
+      <c r="O12">
         <v>2.7708333333333339</v>
       </c>
-      <c r="P11">
+      <c r="P12">
         <v>1.4932055111111457</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14">
-        <v>22.571428571428573</v>
-      </c>
-      <c r="H14">
-        <v>2.2808728487973529</v>
-      </c>
-      <c r="I14">
-        <v>20.714285714285715</v>
-      </c>
-      <c r="J14">
-        <v>1.8224786888818676</v>
-      </c>
-      <c r="K14">
-        <v>25.071428571428573</v>
-      </c>
-      <c r="L14">
-        <v>3.2071349029490825</v>
-      </c>
-      <c r="M14">
-        <v>22.785714285714288</v>
-      </c>
-      <c r="N14">
-        <v>1.2572540835836763</v>
-      </c>
-      <c r="O14">
-        <v>2.6428571428571432</v>
-      </c>
-      <c r="P14">
-        <v>1.8669359216239139</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>23.5</v>
+        <v>22.571428571428573</v>
       </c>
       <c r="H15">
-        <v>2.5495097567963922</v>
+        <v>2.2808728487973529</v>
       </c>
       <c r="I15">
-        <v>19</v>
+        <v>20.714285714285715</v>
       </c>
       <c r="J15">
-        <v>4.0373258476372698</v>
+        <v>1.8224786888818676</v>
       </c>
       <c r="K15">
-        <v>19.75</v>
+        <v>25.071428571428573</v>
       </c>
       <c r="L15">
-        <v>1.6046806535881213</v>
+        <v>3.2071349029490825</v>
       </c>
       <c r="M15">
-        <v>20.750000000000004</v>
+        <v>22.785714285714288</v>
       </c>
       <c r="N15">
-        <v>1.7344547654330258</v>
+        <v>1.2572540835836763</v>
       </c>
       <c r="O15">
-        <v>3.2500000000000004</v>
+        <v>2.6428571428571432</v>
       </c>
       <c r="P15">
-        <v>1.6253204812179864</v>
+        <v>1.8669359216239139</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>23.5</v>
+      </c>
+      <c r="H16">
+        <v>2.5495097567963922</v>
+      </c>
+      <c r="I16">
+        <v>19</v>
+      </c>
+      <c r="J16">
+        <v>4.0373258476372698</v>
+      </c>
+      <c r="K16">
+        <v>19.75</v>
+      </c>
+      <c r="L16">
+        <v>1.6046806535881213</v>
+      </c>
+      <c r="M16">
+        <v>20.750000000000004</v>
+      </c>
+      <c r="N16">
+        <v>1.7344547654330258</v>
+      </c>
+      <c r="O16">
+        <v>3.2500000000000004</v>
+      </c>
+      <c r="P16">
+        <v>1.6253204812179864</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>21.85</v>
-      </c>
-      <c r="H17">
-        <v>1.8112303982529545</v>
-      </c>
-      <c r="I17">
-        <v>19.3</v>
-      </c>
-      <c r="J17">
-        <v>2.3828088000882</v>
-      </c>
-      <c r="K17">
-        <v>21.3</v>
-      </c>
-      <c r="L17">
-        <v>3.2846444082866761</v>
-      </c>
-      <c r="M17">
-        <v>20.81666666666667</v>
-      </c>
-      <c r="N17">
-        <v>1.5425047771901135</v>
-      </c>
-      <c r="O17">
-        <v>2.4166666666666661</v>
-      </c>
-      <c r="P17">
-        <v>1.0191075737691182</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18">
+        <v>21.85</v>
+      </c>
+      <c r="H18">
+        <v>1.8112303982529545</v>
+      </c>
+      <c r="I18">
+        <v>19.3</v>
+      </c>
+      <c r="J18">
+        <v>2.3828088000882</v>
+      </c>
+      <c r="K18">
+        <v>21.3</v>
+      </c>
+      <c r="L18">
+        <v>3.2846444082866761</v>
+      </c>
+      <c r="M18">
+        <v>20.81666666666667</v>
+      </c>
+      <c r="N18">
+        <v>1.5425047771901135</v>
+      </c>
+      <c r="O18">
+        <v>2.4166666666666661</v>
+      </c>
+      <c r="P18">
+        <v>1.0191075737691182</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
         <v>66</v>
       </c>
-      <c r="G19">
+      <c r="G20">
         <v>23.75</v>
       </c>
-      <c r="H19">
+      <c r="H20">
         <v>3.5237290853109955</v>
       </c>
-      <c r="I19">
+      <c r="I20">
         <v>22.5</v>
       </c>
-      <c r="J19">
+      <c r="J20">
         <v>0.40824829046386302</v>
       </c>
-      <c r="K19">
+      <c r="K20">
         <v>21.75</v>
       </c>
-      <c r="L19">
+      <c r="L20">
         <v>3.662876829305985</v>
       </c>
-      <c r="M19">
+      <c r="M20">
         <v>22.666666666666664</v>
       </c>
-      <c r="N19">
+      <c r="N20">
         <v>2.3053882134718262</v>
       </c>
-      <c r="O19">
+      <c r="O20">
         <v>1.9166666666666661</v>
       </c>
-      <c r="P19">
+      <c r="P20">
         <v>0.67357531405456328</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22">
-        <v>19.333333333333332</v>
-      </c>
-      <c r="H22">
-        <v>2.2730302828309825</v>
-      </c>
-      <c r="I22">
-        <v>16.083333333333332</v>
-      </c>
-      <c r="J22">
-        <v>2.5964719653149833</v>
-      </c>
-      <c r="K22">
-        <v>24.083333333333332</v>
-      </c>
-      <c r="L22">
-        <v>1.9343388189938875</v>
-      </c>
-      <c r="M22">
-        <v>19.833333333333332</v>
-      </c>
-      <c r="N22">
-        <v>1.4220486005134358</v>
-      </c>
-      <c r="O22">
-        <v>3.75</v>
-      </c>
-      <c r="P22">
-        <v>2.0076243561870726</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>21.3</v>
+        <v>19.333333333333332</v>
       </c>
       <c r="H23">
-        <v>1.6807736313971611</v>
+        <v>2.2730302828309825</v>
       </c>
       <c r="I23">
-        <v>17.7</v>
+        <v>16.083333333333332</v>
       </c>
       <c r="J23">
-        <v>4.2514703338962612</v>
+        <v>2.5964719653149833</v>
       </c>
       <c r="K23">
-        <v>21.8</v>
+        <v>24.083333333333332</v>
       </c>
       <c r="L23">
-        <v>1.2041594578792296</v>
+        <v>1.9343388189938875</v>
       </c>
       <c r="M23">
-        <v>20.266666666666666</v>
+        <v>19.833333333333332</v>
       </c>
       <c r="N23">
-        <v>1.9811612756158954</v>
+        <v>1.4220486005134358</v>
       </c>
       <c r="O23">
-        <v>2.8666666666666663</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>2.0186629238186353</v>
+        <v>2.0076243561870726</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>21.3</v>
+      </c>
+      <c r="H24">
+        <v>1.6807736313971611</v>
+      </c>
+      <c r="I24">
+        <v>17.7</v>
+      </c>
+      <c r="J24">
+        <v>4.2514703338962612</v>
+      </c>
+      <c r="K24">
+        <v>21.8</v>
+      </c>
+      <c r="L24">
+        <v>1.2041594578792296</v>
+      </c>
+      <c r="M24">
+        <v>20.266666666666666</v>
+      </c>
+      <c r="N24">
+        <v>1.9811612756158954</v>
+      </c>
+      <c r="O24">
+        <v>2.8666666666666663</v>
+      </c>
+      <c r="P24">
+        <v>2.0186629238186353</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E26" t="s">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
         <v>66</v>
       </c>
-      <c r="G26">
+      <c r="G27">
         <v>23.833333333333332</v>
       </c>
-      <c r="H26">
+      <c r="H27">
         <v>1.0408329997330663</v>
       </c>
-      <c r="I26">
+      <c r="I27">
         <v>20</v>
       </c>
-      <c r="J26">
+      <c r="J27">
         <v>4.5</v>
       </c>
-      <c r="K26">
+      <c r="K27">
         <v>23.5</v>
       </c>
-      <c r="L26">
+      <c r="L27">
         <v>1.3228756555322954</v>
       </c>
-      <c r="M26">
+      <c r="M27">
         <v>22.444444444444446</v>
       </c>
-      <c r="N26">
+      <c r="N27">
         <v>1.4369463507086175</v>
       </c>
-      <c r="O26">
+      <c r="O27">
         <v>3.111111111111112</v>
       </c>
-      <c r="P26">
+      <c r="P27">
         <v>2.2381374531648541</v>
       </c>
     </row>
@@ -5113,7 +5151,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -5466,6 +5504,237 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>1.1666666666666679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>91</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>64</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>86</v>
+      </c>
+      <c r="L9">
+        <v>76</v>
+      </c>
+      <c r="M9">
+        <v>24</v>
+      </c>
+      <c r="N9">
+        <v>18</v>
+      </c>
+      <c r="O9">
+        <v>82</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q8:Q11" si="6">AVERAGE(C9:D9)</f>
+        <v>22.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R8:R11" si="7">AVERAGE(H9:I9)</f>
+        <v>19.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S8:S11" si="8">AVERAGE(M9:N9)</f>
+        <v>21</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T8:T11" si="9">AVERAGE(Q9:S9)</f>
+        <v>21</v>
+      </c>
+      <c r="U9">
+        <f>AVERAGE(Q9:Q12)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="V9">
+        <f>_xlfn.STDEV.S(Q9:Q12)</f>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="W9">
+        <f>AVERAGE(R9:R12)</f>
+        <v>20.5</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.STDEV.S(R9:R12)</f>
+        <v>5.0744457825461096</v>
+      </c>
+      <c r="Y9">
+        <f>AVERAGE(S9:S12)</f>
+        <v>24.5</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.STDEV.S(S9:S12)</f>
+        <v>3.0413812651491097</v>
+      </c>
+      <c r="AA9">
+        <f>AVERAGE(T9:T12)</f>
+        <v>22.388888888888886</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.STDEV.S(T9:T12)</f>
+        <v>2.1235016504018209</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC8:AC11" si="10">MIN(Q9:S9)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD8:AD11" si="11">T9-AC9</f>
+        <v>1.5</v>
+      </c>
+      <c r="AE9">
+        <f>AVERAGE(AD9:AD12)</f>
+        <v>3.0555555555555549</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.STDEV.S(AD9:AD12)</f>
+        <v>2.0161385901804505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>92</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>37</v>
+      </c>
+      <c r="E10">
+        <v>63</v>
+      </c>
+      <c r="G10">
+        <v>68</v>
+      </c>
+      <c r="H10">
+        <v>32</v>
+      </c>
+      <c r="I10">
+        <v>20</v>
+      </c>
+      <c r="J10">
+        <v>80</v>
+      </c>
+      <c r="L10">
+        <v>76</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
+      </c>
+      <c r="N10">
+        <v>28</v>
+      </c>
+      <c r="O10">
+        <v>72</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>22.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="8"/>
+        <v>26</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>24.833333333333332</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="10"/>
+        <v>22.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="11"/>
+        <v>2.3333333333333321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>90</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>67</v>
+      </c>
+      <c r="G11">
+        <v>83</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <v>15</v>
+      </c>
+      <c r="J11">
+        <v>85</v>
+      </c>
+      <c r="L11">
+        <v>80</v>
+      </c>
+      <c r="M11">
+        <v>20</v>
+      </c>
+      <c r="N11">
+        <v>33</v>
+      </c>
+      <c r="O11">
+        <v>67</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>21.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>26.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>5.3333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -11631,19 +11900,19 @@
         <v>83</v>
       </c>
       <c r="Q15">
-        <f t="shared" ref="Q14:Q16" si="6">AVERAGE(C15:D15)</f>
+        <f t="shared" ref="Q15:Q16" si="6">AVERAGE(C15:D15)</f>
         <v>22.5</v>
       </c>
       <c r="R15">
-        <f t="shared" ref="R14:R16" si="7">AVERAGE(H15:I15)</f>
+        <f t="shared" ref="R15:R16" si="7">AVERAGE(H15:I15)</f>
         <v>14.5</v>
       </c>
       <c r="S15">
-        <f t="shared" ref="S14:S16" si="8">AVERAGE(M15:N15)</f>
+        <f t="shared" ref="S15:S16" si="8">AVERAGE(M15:N15)</f>
         <v>22.5</v>
       </c>
       <c r="T15">
-        <f t="shared" ref="T14:T16" si="9">AVERAGE(Q15:S15)</f>
+        <f t="shared" ref="T15:T16" si="9">AVERAGE(Q15:S15)</f>
         <v>19.833333333333332</v>
       </c>
       <c r="U15">
@@ -11679,11 +11948,11 @@
         <v>2.0034692133618863</v>
       </c>
       <c r="AC15">
-        <f t="shared" ref="AC14:AC16" si="10">MIN(Q15:S15)</f>
+        <f t="shared" ref="AC15:AC16" si="10">MIN(Q15:S15)</f>
         <v>14.5</v>
       </c>
       <c r="AD15">
-        <f t="shared" ref="AD14:AD16" si="11">T15-AC15</f>
+        <f t="shared" ref="AD15:AD16" si="11">T15-AC15</f>
         <v>5.3333333333333321</v>
       </c>
       <c r="AE15">

--- a/DataAnalysis/CS/0.05/Results.xlsx
+++ b/DataAnalysis/CS/0.05/Results.xlsx
@@ -1,35 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CS\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD82391-C29B-4B0B-9392-4B45BAA42556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF60B16-DC22-4492-A2B5-E22ED204F6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId6"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId7"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId8"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId9"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId10"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId11"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId12"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId13"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId15"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId16"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId17"/>
+    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId2"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId4"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId8"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId9"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId11"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="73">
   <si>
     <t>Dati originali</t>
   </si>
@@ -588,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1060,166 +1061,309 @@
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19">
+        <v>26.6</v>
+      </c>
+      <c r="H19">
+        <v>2.8809720581775866</v>
+      </c>
+      <c r="I19">
+        <v>17.2</v>
+      </c>
+      <c r="J19">
+        <v>3.5106979363083899</v>
+      </c>
+      <c r="K19">
+        <v>21.4</v>
+      </c>
+      <c r="L19">
+        <v>2.6076809620810506</v>
+      </c>
+      <c r="M19">
+        <v>21.733333333333334</v>
+      </c>
+      <c r="N19">
+        <v>1.2281422284627033</v>
+      </c>
+      <c r="O19">
+        <v>4.8333333333333339</v>
+      </c>
+      <c r="P19">
+        <v>2.4152294576982389</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E20" t="s">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
         <v>66</v>
       </c>
-      <c r="G20">
+      <c r="G21">
         <v>23.75</v>
       </c>
-      <c r="H20">
+      <c r="H21">
         <v>3.5237290853109955</v>
       </c>
-      <c r="I20">
+      <c r="I21">
         <v>22.5</v>
       </c>
-      <c r="J20">
+      <c r="J21">
         <v>0.40824829046386302</v>
       </c>
-      <c r="K20">
+      <c r="K21">
         <v>21.75</v>
       </c>
-      <c r="L20">
+      <c r="L21">
         <v>3.662876829305985</v>
       </c>
-      <c r="M20">
+      <c r="M21">
         <v>22.666666666666664</v>
       </c>
-      <c r="N20">
+      <c r="N21">
         <v>2.3053882134718262</v>
       </c>
-      <c r="O20">
+      <c r="O21">
         <v>1.9166666666666661</v>
       </c>
-      <c r="P20">
+      <c r="P21">
         <v>0.67357531405456328</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22">
+        <v>25.625</v>
+      </c>
+      <c r="H22">
+        <v>3.3260336739125176</v>
+      </c>
+      <c r="I22">
+        <v>19.125</v>
+      </c>
+      <c r="J22">
+        <v>0.62915286960589578</v>
+      </c>
+      <c r="K22">
+        <v>17.875</v>
+      </c>
+      <c r="L22">
+        <v>3.0923292192132452</v>
+      </c>
+      <c r="M22">
+        <v>20.875</v>
+      </c>
+      <c r="N22">
+        <v>1.3289859682117418</v>
+      </c>
+      <c r="O22">
+        <v>3.625</v>
+      </c>
+      <c r="P22">
+        <v>1.5949863577728434</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23">
-        <v>19.333333333333332</v>
-      </c>
-      <c r="H23">
-        <v>2.2730302828309825</v>
-      </c>
-      <c r="I23">
-        <v>16.083333333333332</v>
-      </c>
-      <c r="J23">
-        <v>2.5964719653149833</v>
-      </c>
-      <c r="K23">
-        <v>24.083333333333332</v>
-      </c>
-      <c r="L23">
-        <v>1.9343388189938875</v>
-      </c>
-      <c r="M23">
-        <v>19.833333333333332</v>
-      </c>
-      <c r="N23">
-        <v>1.4220486005134358</v>
-      </c>
-      <c r="O23">
-        <v>3.75</v>
-      </c>
-      <c r="P23">
-        <v>2.0076243561870726</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24">
-        <v>21.3</v>
-      </c>
-      <c r="H24">
-        <v>1.6807736313971611</v>
-      </c>
-      <c r="I24">
-        <v>17.7</v>
-      </c>
-      <c r="J24">
-        <v>4.2514703338962612</v>
-      </c>
-      <c r="K24">
-        <v>21.8</v>
-      </c>
-      <c r="L24">
-        <v>1.2041594578792296</v>
-      </c>
-      <c r="M24">
-        <v>20.266666666666666</v>
-      </c>
-      <c r="N24">
-        <v>1.9811612756158954</v>
-      </c>
-      <c r="O24">
-        <v>2.8666666666666663</v>
-      </c>
-      <c r="P24">
-        <v>2.0186629238186353</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>19.333333333333332</v>
+      </c>
+      <c r="H25">
+        <v>2.2730302828309825</v>
+      </c>
+      <c r="I25">
+        <v>16.083333333333332</v>
+      </c>
+      <c r="J25">
+        <v>2.5964719653149833</v>
+      </c>
+      <c r="K25">
+        <v>24.083333333333332</v>
+      </c>
+      <c r="L25">
+        <v>1.9343388189938875</v>
+      </c>
+      <c r="M25">
+        <v>19.833333333333332</v>
+      </c>
+      <c r="N25">
+        <v>1.4220486005134358</v>
+      </c>
+      <c r="O25">
+        <v>3.75</v>
+      </c>
+      <c r="P25">
+        <v>2.0076243561870726</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>21.3</v>
+      </c>
+      <c r="H26">
+        <v>1.6807736313971611</v>
+      </c>
+      <c r="I26">
+        <v>17.7</v>
+      </c>
+      <c r="J26">
+        <v>4.2514703338962612</v>
+      </c>
+      <c r="K26">
+        <v>21.8</v>
+      </c>
+      <c r="L26">
+        <v>1.2041594578792296</v>
+      </c>
+      <c r="M26">
+        <v>20.266666666666666</v>
+      </c>
+      <c r="N26">
+        <v>1.9811612756158954</v>
+      </c>
+      <c r="O26">
+        <v>2.8666666666666663</v>
+      </c>
+      <c r="P26">
+        <v>2.0186629238186353</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D26" t="s">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28">
+        <v>23</v>
+      </c>
+      <c r="H28">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="I28">
+        <v>13.25</v>
+      </c>
+      <c r="J28">
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="K28">
+        <v>22.75</v>
+      </c>
+      <c r="L28">
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="M28">
+        <v>19.666666666666664</v>
+      </c>
+      <c r="N28">
+        <v>0.23570226039551501</v>
+      </c>
+      <c r="O28">
+        <v>6.4166666666666661</v>
+      </c>
+      <c r="P28">
+        <v>2.7105759945484333</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E27" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
         <v>66</v>
       </c>
-      <c r="G27">
+      <c r="G30">
         <v>23.833333333333332</v>
       </c>
-      <c r="H27">
+      <c r="H30">
         <v>1.0408329997330663</v>
       </c>
-      <c r="I27">
+      <c r="I30">
         <v>20</v>
       </c>
-      <c r="J27">
+      <c r="J30">
         <v>4.5</v>
       </c>
-      <c r="K27">
+      <c r="K30">
         <v>23.5</v>
       </c>
-      <c r="L27">
+      <c r="L30">
         <v>1.3228756555322954</v>
       </c>
-      <c r="M27">
+      <c r="M30">
         <v>22.444444444444446</v>
       </c>
-      <c r="N27">
+      <c r="N30">
         <v>1.4369463507086175</v>
       </c>
-      <c r="O27">
+      <c r="O30">
         <v>3.111111111111112</v>
       </c>
-      <c r="P27">
+      <c r="P30">
         <v>2.2381374531648541</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31">
+        <v>22.75</v>
+      </c>
+      <c r="H31">
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="I31">
+        <v>19.5</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>21.5</v>
+      </c>
+      <c r="L31">
+        <v>6.3639610306789276</v>
+      </c>
+      <c r="M31">
+        <v>21.25</v>
+      </c>
+      <c r="N31">
+        <v>1.5320646925708512</v>
+      </c>
+      <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="P31">
+        <v>0.2357022603955175</v>
       </c>
     </row>
   </sheetData>
@@ -1229,6 +1373,557 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
+  <dimension ref="A2:AF10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>90</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>64</v>
+      </c>
+      <c r="G4">
+        <v>74</v>
+      </c>
+      <c r="H4">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>87</v>
+      </c>
+      <c r="L4">
+        <v>80</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>24</v>
+      </c>
+      <c r="O4">
+        <v>76</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>23</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>19.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>22</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>21.5</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q10)</f>
+        <v>22.571428571428573</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q10)</f>
+        <v>2.2808728487973529</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R10)</f>
+        <v>20.714285714285715</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R10)</f>
+        <v>1.8224786888818676</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S10)</f>
+        <v>25.071428571428573</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S10)</f>
+        <v>3.2071349029490825</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T10)</f>
+        <v>22.785714285714288</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T10)</f>
+        <v>1.2572540835836763</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>2</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD10)</f>
+        <v>2.6428571428571432</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD10)</f>
+        <v>1.8669359216239139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>89</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>29</v>
+      </c>
+      <c r="E5">
+        <v>71</v>
+      </c>
+      <c r="G5">
+        <v>62</v>
+      </c>
+      <c r="H5">
+        <v>38</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>91</v>
+      </c>
+      <c r="L5">
+        <v>69</v>
+      </c>
+      <c r="M5">
+        <v>31</v>
+      </c>
+      <c r="N5">
+        <v>24</v>
+      </c>
+      <c r="O5">
+        <v>76</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
+        <v>20</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
+        <v>23.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
+        <v>27.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC10" si="4">MIN(Q5:S5)</f>
+        <v>20</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD10" si="5">T5-AC5</f>
+        <v>3.6666666666666679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>89</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>69</v>
+      </c>
+      <c r="G6">
+        <v>74</v>
+      </c>
+      <c r="H6">
+        <v>26</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>87</v>
+      </c>
+      <c r="L6">
+        <v>76</v>
+      </c>
+      <c r="M6">
+        <v>24</v>
+      </c>
+      <c r="N6">
+        <v>22</v>
+      </c>
+      <c r="O6">
+        <v>78</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>19.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>1.6666666666666679</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>92</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>67</v>
+      </c>
+      <c r="G7">
+        <v>74</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>14</v>
+      </c>
+      <c r="J7">
+        <v>86</v>
+      </c>
+      <c r="L7">
+        <v>71</v>
+      </c>
+      <c r="M7">
+        <v>29</v>
+      </c>
+      <c r="N7">
+        <v>26</v>
+      </c>
+      <c r="O7">
+        <v>74</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>2.6666666666666679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>94</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>44</v>
+      </c>
+      <c r="E8">
+        <v>56</v>
+      </c>
+      <c r="G8">
+        <v>71</v>
+      </c>
+      <c r="H8">
+        <v>29</v>
+      </c>
+      <c r="I8">
+        <v>16</v>
+      </c>
+      <c r="J8">
+        <v>84</v>
+      </c>
+      <c r="L8">
+        <v>81</v>
+      </c>
+      <c r="M8">
+        <v>19</v>
+      </c>
+      <c r="N8">
+        <v>25</v>
+      </c>
+      <c r="O8">
+        <v>75</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>22.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>1.1666666666666679</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>90</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>58</v>
+      </c>
+      <c r="G9">
+        <v>79</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>16</v>
+      </c>
+      <c r="J9">
+        <v>84</v>
+      </c>
+      <c r="L9">
+        <v>78</v>
+      </c>
+      <c r="M9">
+        <v>22</v>
+      </c>
+      <c r="N9">
+        <v>38</v>
+      </c>
+      <c r="O9">
+        <v>62</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>24.833333333333332</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>18.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>6.3333333333333321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>87</v>
+      </c>
+      <c r="C10">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>32</v>
+      </c>
+      <c r="E10">
+        <v>68</v>
+      </c>
+      <c r="G10">
+        <v>70</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
+      <c r="I10">
+        <v>13</v>
+      </c>
+      <c r="J10">
+        <v>87</v>
+      </c>
+      <c r="L10">
+        <v>70</v>
+      </c>
+      <c r="M10">
+        <v>30</v>
+      </c>
+      <c r="N10">
+        <v>17</v>
+      </c>
+      <c r="O10">
+        <v>83</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>23.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>22.5</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>21.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1714,7 +2409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AN99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4417,7 +5112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5149,7 +5844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5549,19 +6244,19 @@
         <v>82</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q8:Q11" si="6">AVERAGE(C9:D9)</f>
+        <f t="shared" ref="Q9:Q11" si="6">AVERAGE(C9:D9)</f>
         <v>22.5</v>
       </c>
       <c r="R9">
-        <f t="shared" ref="R8:R11" si="7">AVERAGE(H9:I9)</f>
+        <f t="shared" ref="R9:R11" si="7">AVERAGE(H9:I9)</f>
         <v>19.5</v>
       </c>
       <c r="S9">
-        <f t="shared" ref="S8:S11" si="8">AVERAGE(M9:N9)</f>
+        <f t="shared" ref="S9:S11" si="8">AVERAGE(M9:N9)</f>
         <v>21</v>
       </c>
       <c r="T9">
-        <f t="shared" ref="T8:T11" si="9">AVERAGE(Q9:S9)</f>
+        <f t="shared" ref="T9:T11" si="9">AVERAGE(Q9:S9)</f>
         <v>21</v>
       </c>
       <c r="U9">
@@ -5597,11 +6292,11 @@
         <v>2.1235016504018209</v>
       </c>
       <c r="AC9">
-        <f t="shared" ref="AC8:AC11" si="10">MIN(Q9:S9)</f>
+        <f t="shared" ref="AC9:AC11" si="10">MIN(Q9:S9)</f>
         <v>19.5</v>
       </c>
       <c r="AD9">
-        <f t="shared" ref="AD8:AD11" si="11">T9-AC9</f>
+        <f t="shared" ref="AD9:AD11" si="11">T9-AC9</f>
         <v>1.5</v>
       </c>
       <c r="AE9">
@@ -5742,7 +6437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AR14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6681,7 +7376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AR14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7620,7 +8315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9996,7 +10691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10295,363 +10990,222 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F502F8F-7F4F-4035-A5E9-9B448496FCE0}">
+  <dimension ref="B1:AF3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" t="s">
+    <row r="1" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R1" t="s">
         <v>13</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U1" t="s">
         <v>54</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V1" t="s">
         <v>47</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W1" t="s">
         <v>55</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X1" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y1" t="s">
         <v>56</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z1" t="s">
         <v>49</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA1" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB1" t="s">
         <v>17</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC1" t="s">
         <v>18</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD1" t="s">
         <v>15</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE1" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>93</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>60</v>
+      </c>
+      <c r="G2">
+        <v>91</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>86</v>
+      </c>
+      <c r="L2">
+        <v>85</v>
+      </c>
+      <c r="M2">
+        <v>15</v>
+      </c>
+      <c r="N2">
+        <v>34</v>
+      </c>
+      <c r="O2">
+        <v>66</v>
+      </c>
+      <c r="Q2">
+        <f>AVERAGE(C2,D2)</f>
+        <v>23.5</v>
+      </c>
+      <c r="R2">
+        <f>AVERAGE(H2,I2)</f>
+        <v>11.5</v>
+      </c>
+      <c r="S2">
+        <f>AVERAGE(M2,N2)</f>
+        <v>24.5</v>
+      </c>
+      <c r="T2">
+        <f t="shared" ref="T2" si="0">AVERAGE(Q2:S2)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U2">
+        <f>AVERAGE(Q2:Q5)</f>
         <v>23</v>
       </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>91</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>37</v>
-      </c>
-      <c r="E4">
-        <v>63</v>
-      </c>
-      <c r="G4">
-        <v>74</v>
-      </c>
-      <c r="H4">
-        <v>26</v>
-      </c>
-      <c r="I4">
-        <v>19</v>
-      </c>
-      <c r="J4">
-        <v>81</v>
-      </c>
-      <c r="L4">
+      <c r="V2">
+        <f>_xlfn.STDEV.S(Q2:Q5)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGE(R2:R6)</f>
+        <v>13.25</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.STDEV.S(R2:R5)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGE(S2:S5)</f>
+        <v>22.75</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.STDEV.S(S2:S5)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="AA2">
+        <f>AVERAGE(T2:T5)</f>
+        <v>19.666666666666664</v>
+      </c>
+      <c r="AB2">
+        <f>_xlfn.STDEV.S(T2:T5)</f>
+        <v>0.23570226039551501</v>
+      </c>
+      <c r="AC2">
+        <f>MIN(Q2:S2)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AD2">
+        <f>T2-AC2</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="AE2">
+        <f>AVERAGE(AD2:AD5)</f>
+        <v>6.4166666666666661</v>
+      </c>
+      <c r="AF2">
+        <f>_xlfn.STDEV.S(AD2:AD5)</f>
+        <v>2.7105759945484333</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>85</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>70</v>
+      </c>
+      <c r="G3">
+        <v>78</v>
+      </c>
+      <c r="H3">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>92</v>
+      </c>
+      <c r="L3">
+        <v>78</v>
+      </c>
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3">
+        <v>20</v>
+      </c>
+      <c r="O3">
         <v>80</v>
       </c>
-      <c r="M4">
-        <v>20</v>
-      </c>
-      <c r="N4">
-        <v>20</v>
-      </c>
-      <c r="O4">
-        <v>80</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>23</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
+      <c r="Q3">
+        <f>AVERAGE(C3,D3)</f>
         <v>22.5</v>
       </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>20</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>21.833333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q7)</f>
-        <v>23.75</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q7)</f>
-        <v>3.5237290853109955</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R8)</f>
-        <v>22.5</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R7)</f>
-        <v>0.40824829046386302</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S7)</f>
-        <v>21.75</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S7)</f>
-        <v>3.662876829305985</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T7)</f>
-        <v>22.666666666666664</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T7)</f>
-        <v>2.3053882134718262</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>20</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>1.8333333333333321</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD7)</f>
-        <v>1.9166666666666661</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD7)</f>
-        <v>0.67357531405456328</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>91</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>48</v>
-      </c>
-      <c r="E5">
-        <v>52</v>
-      </c>
-      <c r="G5">
-        <v>77</v>
-      </c>
-      <c r="H5">
-        <v>23</v>
-      </c>
-      <c r="I5">
-        <v>22</v>
-      </c>
-      <c r="J5">
-        <v>78</v>
-      </c>
-      <c r="L5">
-        <v>81</v>
-      </c>
-      <c r="M5">
-        <v>19</v>
-      </c>
-      <c r="N5">
-        <v>29</v>
-      </c>
-      <c r="O5">
-        <v>71</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q7" si="0">AVERAGE(C5,D5)</f>
-        <v>28.5</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R7" si="1">AVERAGE(H5,I5)</f>
-        <v>22.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S7" si="2">AVERAGE(M5,N5)</f>
-        <v>24</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
-        <v>25</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC7" si="4">MIN(Q5:S5)</f>
-        <v>22.5</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD7" si="5">T5-AC5</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>92</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>39</v>
-      </c>
-      <c r="E6">
-        <v>61</v>
-      </c>
-      <c r="G6">
-        <v>78</v>
-      </c>
-      <c r="H6">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>24</v>
-      </c>
-      <c r="J6">
-        <v>76</v>
-      </c>
-      <c r="L6">
-        <v>88</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-      <c r="N6">
-        <v>39</v>
-      </c>
-      <c r="O6">
-        <v>61</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>23.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>25.5</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>23</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <v>82</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>78</v>
-      </c>
-      <c r="G7">
-        <v>74</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
-      <c r="I7">
-        <v>18</v>
-      </c>
-      <c r="J7">
-        <v>82</v>
-      </c>
-      <c r="L7">
-        <v>77</v>
-      </c>
-      <c r="M7">
-        <v>23</v>
-      </c>
-      <c r="N7">
-        <v>12</v>
-      </c>
-      <c r="O7">
-        <v>88</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>17.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>17.5</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>2.3333333333333321</v>
+      <c r="R3">
+        <f>AVERAGE(H3,I3)</f>
+        <v>15</v>
+      </c>
+      <c r="S3">
+        <f>AVERAGE(M3,N3)</f>
+        <v>21</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3" si="1">AVERAGE(Q3:S3)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AC3">
+        <f>MIN(Q3:S3)</f>
+        <v>15</v>
+      </c>
+      <c r="AD3">
+        <f>T3-AC3</f>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -10660,6 +11214,664 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
+  <dimension ref="A2:AF13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>91</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>37</v>
+      </c>
+      <c r="E4">
+        <v>63</v>
+      </c>
+      <c r="G4">
+        <v>74</v>
+      </c>
+      <c r="H4">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>19</v>
+      </c>
+      <c r="J4">
+        <v>81</v>
+      </c>
+      <c r="L4">
+        <v>80</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>20</v>
+      </c>
+      <c r="O4">
+        <v>80</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>23</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>22.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>20</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q7)</f>
+        <v>23.75</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q7)</f>
+        <v>3.5237290853109955</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R8)</f>
+        <v>22.5</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R7)</f>
+        <v>0.40824829046386302</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S7)</f>
+        <v>21.75</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S7)</f>
+        <v>3.662876829305985</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T7)</f>
+        <v>22.666666666666664</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T7)</f>
+        <v>2.3053882134718262</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>20</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>1.8333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD7)</f>
+        <v>1.9166666666666661</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD7)</f>
+        <v>0.67357531405456328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>91</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>52</v>
+      </c>
+      <c r="G5">
+        <v>77</v>
+      </c>
+      <c r="H5">
+        <v>23</v>
+      </c>
+      <c r="I5">
+        <v>22</v>
+      </c>
+      <c r="J5">
+        <v>78</v>
+      </c>
+      <c r="L5">
+        <v>81</v>
+      </c>
+      <c r="M5">
+        <v>19</v>
+      </c>
+      <c r="N5">
+        <v>29</v>
+      </c>
+      <c r="O5">
+        <v>71</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q7" si="0">AVERAGE(C5,D5)</f>
+        <v>28.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R7" si="1">AVERAGE(H5,I5)</f>
+        <v>22.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S7" si="2">AVERAGE(M5,N5)</f>
+        <v>24</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
+        <v>25</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC7" si="4">MIN(Q5:S5)</f>
+        <v>22.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD7" si="5">T5-AC5</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>92</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>39</v>
+      </c>
+      <c r="E6">
+        <v>61</v>
+      </c>
+      <c r="G6">
+        <v>78</v>
+      </c>
+      <c r="H6">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>24</v>
+      </c>
+      <c r="J6">
+        <v>76</v>
+      </c>
+      <c r="L6">
+        <v>88</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+      <c r="N6">
+        <v>39</v>
+      </c>
+      <c r="O6">
+        <v>61</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>23.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>82</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>78</v>
+      </c>
+      <c r="G7">
+        <v>74</v>
+      </c>
+      <c r="H7">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>82</v>
+      </c>
+      <c r="L7">
+        <v>77</v>
+      </c>
+      <c r="M7">
+        <v>23</v>
+      </c>
+      <c r="N7">
+        <v>12</v>
+      </c>
+      <c r="O7">
+        <v>88</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>17.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>2.3333333333333321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>89</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>64</v>
+      </c>
+      <c r="G10">
+        <v>81</v>
+      </c>
+      <c r="H10">
+        <v>19</v>
+      </c>
+      <c r="I10">
+        <v>19</v>
+      </c>
+      <c r="J10">
+        <v>81</v>
+      </c>
+      <c r="L10">
+        <v>76</v>
+      </c>
+      <c r="M10">
+        <v>24</v>
+      </c>
+      <c r="N10">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>81</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C10,D10)</f>
+        <v>23.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R8:R13" si="7">AVERAGE(H10,I10)</f>
+        <v>19</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S8:S13" si="8">AVERAGE(M10,N10)</f>
+        <v>21.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q10:S10)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U10">
+        <f>AVERAGE(Q10:Q13)</f>
+        <v>25.625</v>
+      </c>
+      <c r="V10">
+        <f>_xlfn.STDEV.S(Q10:Q13)</f>
+        <v>3.3260336739125176</v>
+      </c>
+      <c r="W10">
+        <f>AVERAGE(R10:R14)</f>
+        <v>19.125</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.STDEV.S(R10:R13)</f>
+        <v>0.62915286960589578</v>
+      </c>
+      <c r="Y10">
+        <f>AVERAGE(S10:S13)</f>
+        <v>17.875</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.STDEV.S(S10:S13)</f>
+        <v>3.0923292192132452</v>
+      </c>
+      <c r="AA10">
+        <f>AVERAGE(T10:T13)</f>
+        <v>20.875</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.STDEV.S(T10:T13)</f>
+        <v>1.3289859682117418</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" ref="AC8:AC13" si="10">MIN(Q10:S10)</f>
+        <v>19</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" ref="AD8:AD13" si="11">T10-AC10</f>
+        <v>2.3333333333333321</v>
+      </c>
+      <c r="AE10">
+        <f>AVERAGE(AD10:AD13)</f>
+        <v>3.625</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.STDEV.S(AD10:AD13)</f>
+        <v>1.5949863577728434</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>89</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>39</v>
+      </c>
+      <c r="E11">
+        <v>61</v>
+      </c>
+      <c r="G11">
+        <v>79</v>
+      </c>
+      <c r="H11">
+        <v>21</v>
+      </c>
+      <c r="I11">
+        <v>16</v>
+      </c>
+      <c r="J11">
+        <v>84</v>
+      </c>
+      <c r="L11">
+        <v>81</v>
+      </c>
+      <c r="M11">
+        <v>19</v>
+      </c>
+      <c r="N11">
+        <v>18</v>
+      </c>
+      <c r="O11">
+        <v>82</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>18.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>18.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>2.1666666666666679</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>93</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>54</v>
+      </c>
+      <c r="E12">
+        <v>46</v>
+      </c>
+      <c r="G12">
+        <v>83</v>
+      </c>
+      <c r="H12">
+        <v>17</v>
+      </c>
+      <c r="I12">
+        <v>21</v>
+      </c>
+      <c r="J12">
+        <v>79</v>
+      </c>
+      <c r="L12">
+        <v>83</v>
+      </c>
+      <c r="M12">
+        <v>17</v>
+      </c>
+      <c r="N12">
+        <v>18</v>
+      </c>
+      <c r="O12">
+        <v>82</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>30.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>17.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>17.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>4.8333333333333321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>96</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>43</v>
+      </c>
+      <c r="E13">
+        <v>57</v>
+      </c>
+      <c r="G13">
+        <v>75</v>
+      </c>
+      <c r="H13">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <v>85</v>
+      </c>
+      <c r="L13">
+        <v>86</v>
+      </c>
+      <c r="M13">
+        <v>14</v>
+      </c>
+      <c r="N13">
+        <v>14</v>
+      </c>
+      <c r="O13">
+        <v>86</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>23.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>5.1666666666666679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10825,9 +12037,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11125,905 +12337,173 @@
         <v>23</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" t="s">
-        <v>55</v>
-      </c>
-      <c r="X2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>93</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>41</v>
-      </c>
-      <c r="E4">
-        <v>59</v>
-      </c>
-      <c r="G4">
-        <v>76</v>
-      </c>
-      <c r="H4">
-        <v>24</v>
-      </c>
-      <c r="I4">
-        <v>21</v>
-      </c>
-      <c r="J4">
-        <v>79</v>
-      </c>
-      <c r="L4">
-        <v>83</v>
-      </c>
-      <c r="M4">
-        <v>17</v>
-      </c>
-      <c r="N4">
-        <v>21</v>
-      </c>
-      <c r="O4">
-        <v>79</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4:D4)</f>
-        <v>24</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4:I4)</f>
-        <v>22.5</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4:N4)</f>
-        <v>19</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>21.833333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q13)</f>
-        <v>21.85</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q13)</f>
-        <v>1.8112303982529545</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R13)</f>
-        <v>19.3</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R13)</f>
-        <v>2.3828088000882</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S13)</f>
-        <v>21.3</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S13)</f>
-        <v>3.2846444082866761</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T13)</f>
-        <v>20.81666666666667</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T13)</f>
-        <v>1.5425047771901135</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>19</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>2.8333333333333321</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD13)</f>
-        <v>2.4166666666666661</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD13)</f>
-        <v>1.0191075737691182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>92</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>34</v>
-      </c>
-      <c r="E5">
-        <v>66</v>
-      </c>
-      <c r="G5">
-        <v>76</v>
-      </c>
-      <c r="H5">
-        <v>24</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>86</v>
-      </c>
-      <c r="L5">
-        <v>78</v>
-      </c>
-      <c r="M5">
-        <v>22</v>
-      </c>
-      <c r="N5">
-        <v>14</v>
-      </c>
-      <c r="O5">
-        <v>86</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q13" si="0">AVERAGE(C5:D5)</f>
-        <v>21</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R13" si="1">AVERAGE(H5:I5)</f>
-        <v>19</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S13" si="2">AVERAGE(M5:N5)</f>
-        <v>18</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T13" si="3">AVERAGE(Q5:S5)</f>
-        <v>19.333333333333332</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC13" si="4">MIN(Q5:S5)</f>
-        <v>18</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD13" si="5">T5-AC5</f>
-        <v>1.3333333333333321</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>93</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>32</v>
-      </c>
-      <c r="E6">
-        <v>68</v>
-      </c>
-      <c r="G6">
-        <v>84</v>
-      </c>
-      <c r="H6">
-        <v>16</v>
-      </c>
-      <c r="I6">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>84</v>
-      </c>
-      <c r="L6">
-        <v>74</v>
-      </c>
-      <c r="M6">
-        <v>26</v>
-      </c>
-      <c r="N6">
-        <v>22</v>
-      </c>
-      <c r="O6">
-        <v>78</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>3.8333333333333321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <v>95</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>65</v>
-      </c>
-      <c r="G7">
-        <v>82</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>21</v>
-      </c>
-      <c r="J7">
-        <v>79</v>
-      </c>
-      <c r="L7">
-        <v>80</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
-      </c>
-      <c r="N7">
-        <v>28</v>
-      </c>
-      <c r="O7">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>72</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>19.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>21.166666666666668</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>19.5</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>1.6666666666666679</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>90</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>36</v>
-      </c>
-      <c r="E8">
-        <v>64</v>
-      </c>
-      <c r="G8">
-        <v>78</v>
-      </c>
-      <c r="H8">
-        <v>22</v>
-      </c>
-      <c r="I8">
-        <v>18</v>
-      </c>
-      <c r="J8">
-        <v>82</v>
-      </c>
-      <c r="L8">
-        <v>77</v>
-      </c>
-      <c r="M8">
-        <v>23</v>
-      </c>
-      <c r="N8">
-        <v>22</v>
-      </c>
-      <c r="O8">
-        <v>78</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>22.5</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>21.833333333333332</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>1.8333333333333321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>96</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>36</v>
-      </c>
-      <c r="E9">
-        <v>64</v>
-      </c>
-      <c r="G9">
-        <v>75</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>86</v>
-      </c>
-      <c r="L9">
-        <v>86</v>
-      </c>
-      <c r="M9">
-        <v>14</v>
-      </c>
-      <c r="N9">
-        <v>30</v>
-      </c>
-      <c r="O9">
-        <v>70</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>19.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>20.5</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>19.5</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G10">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H10">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L10">
+        <v>88</v>
+      </c>
+      <c r="M10">
+        <v>12</v>
+      </c>
+      <c r="N10">
+        <v>22</v>
+      </c>
+      <c r="O10">
         <v>78</v>
       </c>
-      <c r="M10">
-        <v>22</v>
-      </c>
-      <c r="N10">
-        <v>11</v>
-      </c>
-      <c r="O10">
-        <v>89</v>
-      </c>
       <c r="Q10">
-        <f t="shared" si="0"/>
-        <v>20.5</v>
+        <f t="shared" ref="Q7:Q11" si="6">AVERAGE(C10:D10)</f>
+        <v>24</v>
       </c>
       <c r="R10">
-        <f t="shared" si="1"/>
-        <v>21</v>
+        <f t="shared" ref="R7:R11" si="7">AVERAGE(H10:I10)</f>
+        <v>19.5</v>
       </c>
       <c r="S10">
-        <f t="shared" si="2"/>
-        <v>16.5</v>
+        <f t="shared" ref="S7:S11" si="8">AVERAGE(M10:N10)</f>
+        <v>17</v>
       </c>
       <c r="T10">
-        <f t="shared" si="3"/>
-        <v>19.333333333333332</v>
+        <f t="shared" ref="T7:T11" si="9">AVERAGE(Q10:S10)</f>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U10">
+        <f>AVERAGE(Q10:Q12)</f>
+        <v>22.75</v>
+      </c>
+      <c r="V10">
+        <f>_xlfn.STDEV.S(Q10:Q12)</f>
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="W10">
+        <f>AVERAGE(R10:R12)</f>
+        <v>19.5</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.STDEV.S(R10:R12)</f>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f>AVERAGE(S10:S12)</f>
+        <v>21.5</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.STDEV.S(S10:S12)</f>
+        <v>6.3639610306789276</v>
+      </c>
+      <c r="AA10">
+        <f>AVERAGE(T10:T12)</f>
+        <v>21.25</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.STDEV.S(T10:T12)</f>
+        <v>1.5320646925708512</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="4"/>
-        <v>16.5</v>
+        <f t="shared" ref="AC7:AC11" si="10">MIN(Q10:S10)</f>
+        <v>17</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="5"/>
-        <v>2.8333333333333321</v>
+        <f t="shared" ref="AD7:AD11" si="11">T10-AC10</f>
+        <v>3.1666666666666679</v>
+      </c>
+      <c r="AE10">
+        <f>AVERAGE(AD10:AD12)</f>
+        <v>3</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.STDEV.S(AD10:AD12)</f>
+        <v>0.2357022603955175</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G11">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="H11">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L11">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="M11">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="N11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O11">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <f t="shared" si="6"/>
+        <v>21.5</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f t="shared" si="7"/>
+        <v>19.5</v>
       </c>
       <c r="S11">
-        <f t="shared" si="2"/>
-        <v>17.5</v>
+        <f t="shared" si="8"/>
+        <v>26</v>
       </c>
       <c r="T11">
-        <f t="shared" si="3"/>
-        <v>18.833333333333332</v>
+        <f t="shared" si="9"/>
+        <v>22.333333333333332</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="4"/>
-        <v>15</v>
+        <f t="shared" si="10"/>
+        <v>19.5</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="5"/>
-        <v>3.8333333333333321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>95</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-      <c r="D12">
-        <v>41</v>
-      </c>
-      <c r="E12">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>87</v>
-      </c>
-      <c r="H12">
-        <v>13</v>
-      </c>
-      <c r="I12">
-        <v>24</v>
-      </c>
-      <c r="J12">
-        <v>76</v>
-      </c>
-      <c r="L12">
-        <v>81</v>
-      </c>
-      <c r="M12">
-        <v>19</v>
-      </c>
-      <c r="N12">
-        <v>28</v>
-      </c>
-      <c r="O12">
-        <v>72</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="1"/>
-        <v>18.5</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="2"/>
-        <v>23.5</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="3"/>
-        <v>21.666666666666668</v>
-      </c>
-      <c r="AC12">
-        <f t="shared" si="4"/>
-        <v>18.5</v>
-      </c>
-      <c r="AD12">
-        <f t="shared" si="5"/>
-        <v>3.1666666666666679</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>89</v>
-      </c>
-      <c r="C13">
-        <v>11</v>
-      </c>
-      <c r="D13">
-        <v>36</v>
-      </c>
-      <c r="E13">
-        <v>64</v>
-      </c>
-      <c r="G13">
-        <v>75</v>
-      </c>
-      <c r="H13">
-        <v>25</v>
-      </c>
-      <c r="I13">
-        <v>19</v>
-      </c>
-      <c r="J13">
-        <v>81</v>
-      </c>
-      <c r="L13">
-        <v>74</v>
-      </c>
-      <c r="M13">
-        <v>26</v>
-      </c>
-      <c r="N13">
-        <v>26</v>
-      </c>
-      <c r="O13">
-        <v>74</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="0"/>
-        <v>23.5</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="2"/>
-        <v>26</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="3"/>
-        <v>23.833333333333332</v>
-      </c>
-      <c r="AC13">
-        <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="AD13">
-        <f t="shared" si="5"/>
-        <v>1.8333333333333321</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>93</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-      <c r="D15">
-        <v>38</v>
-      </c>
-      <c r="E15">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>86</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
-      <c r="I15">
-        <v>15</v>
-      </c>
-      <c r="J15">
-        <v>85</v>
-      </c>
-      <c r="L15">
-        <v>72</v>
-      </c>
-      <c r="M15">
-        <v>28</v>
-      </c>
-      <c r="N15">
-        <v>17</v>
-      </c>
-      <c r="O15">
-        <v>83</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" ref="Q15:Q16" si="6">AVERAGE(C15:D15)</f>
-        <v>22.5</v>
-      </c>
-      <c r="R15">
-        <f t="shared" ref="R15:R16" si="7">AVERAGE(H15:I15)</f>
-        <v>14.5</v>
-      </c>
-      <c r="S15">
-        <f t="shared" ref="S15:S16" si="8">AVERAGE(M15:N15)</f>
-        <v>22.5</v>
-      </c>
-      <c r="T15">
-        <f t="shared" ref="T15:T16" si="9">AVERAGE(Q15:S15)</f>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="U15">
-        <f>AVERAGE(Q15:Q24)</f>
-        <v>25</v>
-      </c>
-      <c r="V15">
-        <f>_xlfn.STDEV.S(Q15:Q24)</f>
-        <v>3.5355339059327378</v>
-      </c>
-      <c r="W15">
-        <f>AVERAGE(R15:R24)</f>
-        <v>17.5</v>
-      </c>
-      <c r="X15">
-        <f>_xlfn.STDEV.S(R15:R24)</f>
-        <v>4.2426406871192848</v>
-      </c>
-      <c r="Y15">
-        <f>AVERAGE(S15:S24)</f>
-        <v>21.25</v>
-      </c>
-      <c r="Z15">
-        <f>_xlfn.STDEV.S(S15:S24)</f>
-        <v>1.7677669529663689</v>
-      </c>
-      <c r="AA15">
-        <f>AVERAGE(T15:T24)</f>
-        <v>21.25</v>
-      </c>
-      <c r="AB15">
-        <f>_xlfn.STDEV.S(T15:T24)</f>
-        <v>2.0034692133618863</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" ref="AC15:AC16" si="10">MIN(Q15:S15)</f>
-        <v>14.5</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" ref="AD15:AD16" si="11">T15-AC15</f>
-        <v>5.3333333333333321</v>
-      </c>
-      <c r="AE15">
-        <f>AVERAGE(AD15:AD24)</f>
-        <v>4</v>
-      </c>
-      <c r="AF15">
-        <f>_xlfn.STDEV.S(AD15:AD24)</f>
-        <v>1.8856180831641252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>91</v>
-      </c>
-      <c r="C16">
-        <v>9</v>
-      </c>
-      <c r="D16">
-        <v>46</v>
-      </c>
-      <c r="E16">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>83</v>
-      </c>
-      <c r="H16">
-        <v>17</v>
-      </c>
-      <c r="I16">
-        <v>24</v>
-      </c>
-      <c r="J16">
-        <v>76</v>
-      </c>
-      <c r="L16">
-        <v>81</v>
-      </c>
-      <c r="M16">
-        <v>19</v>
-      </c>
-      <c r="N16">
-        <v>21</v>
-      </c>
-      <c r="O16">
-        <v>79</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="6"/>
-        <v>27.5</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="7"/>
-        <v>20.5</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="9"/>
-        <v>22.666666666666668</v>
-      </c>
-      <c r="AC16">
-        <f t="shared" si="10"/>
-        <v>20</v>
-      </c>
-      <c r="AD16">
         <f t="shared" si="11"/>
-        <v>2.6666666666666679</v>
+        <v>2.8333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -12032,6 +12512,1262 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
+  <dimension ref="A2:AF30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>93</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>41</v>
+      </c>
+      <c r="E4">
+        <v>59</v>
+      </c>
+      <c r="G4">
+        <v>76</v>
+      </c>
+      <c r="H4">
+        <v>24</v>
+      </c>
+      <c r="I4">
+        <v>21</v>
+      </c>
+      <c r="J4">
+        <v>79</v>
+      </c>
+      <c r="L4">
+        <v>83</v>
+      </c>
+      <c r="M4">
+        <v>17</v>
+      </c>
+      <c r="N4">
+        <v>21</v>
+      </c>
+      <c r="O4">
+        <v>79</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4:D4)</f>
+        <v>24</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4:I4)</f>
+        <v>22.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4:N4)</f>
+        <v>19</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q13)</f>
+        <v>21.85</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q13)</f>
+        <v>1.8112303982529545</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R13)</f>
+        <v>19.3</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R13)</f>
+        <v>2.3828088000882</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S13)</f>
+        <v>21.3</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S13)</f>
+        <v>3.2846444082866761</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T13)</f>
+        <v>20.81666666666667</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T13)</f>
+        <v>1.5425047771901135</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>19</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>2.8333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD13)</f>
+        <v>2.4166666666666661</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD13)</f>
+        <v>1.0191075737691182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>92</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>66</v>
+      </c>
+      <c r="G5">
+        <v>76</v>
+      </c>
+      <c r="H5">
+        <v>24</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>86</v>
+      </c>
+      <c r="L5">
+        <v>78</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>14</v>
+      </c>
+      <c r="O5">
+        <v>86</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q13" si="0">AVERAGE(C5:D5)</f>
+        <v>21</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R13" si="1">AVERAGE(H5:I5)</f>
+        <v>19</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S13" si="2">AVERAGE(M5:N5)</f>
+        <v>18</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T13" si="3">AVERAGE(Q5:S5)</f>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC13" si="4">MIN(Q5:S5)</f>
+        <v>18</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD13" si="5">T5-AC5</f>
+        <v>1.3333333333333321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>93</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+      <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>84</v>
+      </c>
+      <c r="L6">
+        <v>74</v>
+      </c>
+      <c r="M6">
+        <v>26</v>
+      </c>
+      <c r="N6">
+        <v>22</v>
+      </c>
+      <c r="O6">
+        <v>78</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>95</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>82</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>79</v>
+      </c>
+      <c r="L7">
+        <v>80</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+      <c r="N7">
+        <v>28</v>
+      </c>
+      <c r="O7">
+        <v>72</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>19.5</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>1.6666666666666679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>90</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>36</v>
+      </c>
+      <c r="E8">
+        <v>64</v>
+      </c>
+      <c r="G8">
+        <v>78</v>
+      </c>
+      <c r="H8">
+        <v>22</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>82</v>
+      </c>
+      <c r="L8">
+        <v>77</v>
+      </c>
+      <c r="M8">
+        <v>23</v>
+      </c>
+      <c r="N8">
+        <v>22</v>
+      </c>
+      <c r="O8">
+        <v>78</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>96</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>64</v>
+      </c>
+      <c r="G9">
+        <v>75</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>86</v>
+      </c>
+      <c r="L9">
+        <v>86</v>
+      </c>
+      <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>30</v>
+      </c>
+      <c r="O9">
+        <v>70</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>20.5</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>19.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>90</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>31</v>
+      </c>
+      <c r="E10">
+        <v>69</v>
+      </c>
+      <c r="G10">
+        <v>74</v>
+      </c>
+      <c r="H10">
+        <v>26</v>
+      </c>
+      <c r="I10">
+        <v>16</v>
+      </c>
+      <c r="J10">
+        <v>84</v>
+      </c>
+      <c r="L10">
+        <v>78</v>
+      </c>
+      <c r="M10">
+        <v>22</v>
+      </c>
+      <c r="N10">
+        <v>11</v>
+      </c>
+      <c r="O10">
+        <v>89</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>16.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>2.8333333333333321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>91</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>39</v>
+      </c>
+      <c r="E11">
+        <v>61</v>
+      </c>
+      <c r="G11">
+        <v>84</v>
+      </c>
+      <c r="H11">
+        <v>16</v>
+      </c>
+      <c r="I11">
+        <v>14</v>
+      </c>
+      <c r="J11">
+        <v>86</v>
+      </c>
+      <c r="L11">
+        <v>89</v>
+      </c>
+      <c r="M11">
+        <v>11</v>
+      </c>
+      <c r="N11">
+        <v>24</v>
+      </c>
+      <c r="O11">
+        <v>76</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="2"/>
+        <v>17.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="3"/>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="5"/>
+        <v>3.8333333333333321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>41</v>
+      </c>
+      <c r="E12">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>87</v>
+      </c>
+      <c r="H12">
+        <v>13</v>
+      </c>
+      <c r="I12">
+        <v>24</v>
+      </c>
+      <c r="J12">
+        <v>76</v>
+      </c>
+      <c r="L12">
+        <v>81</v>
+      </c>
+      <c r="M12">
+        <v>19</v>
+      </c>
+      <c r="N12">
+        <v>28</v>
+      </c>
+      <c r="O12">
+        <v>72</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>18.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>23.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="4"/>
+        <v>18.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="5"/>
+        <v>3.1666666666666679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>89</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>36</v>
+      </c>
+      <c r="E13">
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <v>75</v>
+      </c>
+      <c r="H13">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>19</v>
+      </c>
+      <c r="J13">
+        <v>81</v>
+      </c>
+      <c r="L13">
+        <v>74</v>
+      </c>
+      <c r="M13">
+        <v>26</v>
+      </c>
+      <c r="N13">
+        <v>26</v>
+      </c>
+      <c r="O13">
+        <v>74</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="0"/>
+        <v>23.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>93</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>62</v>
+      </c>
+      <c r="G15">
+        <v>86</v>
+      </c>
+      <c r="H15">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>15</v>
+      </c>
+      <c r="J15">
+        <v>85</v>
+      </c>
+      <c r="L15">
+        <v>72</v>
+      </c>
+      <c r="M15">
+        <v>28</v>
+      </c>
+      <c r="N15">
+        <v>17</v>
+      </c>
+      <c r="O15">
+        <v>83</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" ref="Q15:Q16" si="6">AVERAGE(C15:D15)</f>
+        <v>22.5</v>
+      </c>
+      <c r="R15">
+        <f t="shared" ref="R15:R16" si="7">AVERAGE(H15:I15)</f>
+        <v>14.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" ref="S15:S16" si="8">AVERAGE(M15:N15)</f>
+        <v>22.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" ref="T15:T16" si="9">AVERAGE(Q15:S15)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U15">
+        <f>AVERAGE(Q15:Q26)</f>
+        <v>24.333333333333332</v>
+      </c>
+      <c r="V15">
+        <f>_xlfn.STDEV.S(Q15:Q26)</f>
+        <v>2.753785273643051</v>
+      </c>
+      <c r="W15">
+        <f>AVERAGE(R15:R26)</f>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="X15">
+        <f>_xlfn.STDEV.S(R15:R26)</f>
+        <v>3.617089069035115</v>
+      </c>
+      <c r="Y15">
+        <f>AVERAGE(S15:S26)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="Z15">
+        <f>_xlfn.STDEV.S(S15:S26)</f>
+        <v>2.0207259421636903</v>
+      </c>
+      <c r="AA15">
+        <f>AVERAGE(T15:T26)</f>
+        <v>20.944444444444443</v>
+      </c>
+      <c r="AB15">
+        <f>_xlfn.STDEV.S(T15:T26)</f>
+        <v>1.5122952876462457</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" ref="AC15:AC16" si="10">MIN(Q15:S15)</f>
+        <v>14.5</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" ref="AD15:AD16" si="11">T15-AC15</f>
+        <v>5.3333333333333321</v>
+      </c>
+      <c r="AE15">
+        <f>AVERAGE(AD15:AD26)</f>
+        <v>4.7777777777777777</v>
+      </c>
+      <c r="AF15">
+        <f>_xlfn.STDEV.S(AD15:AD26)</f>
+        <v>1.8954135676924411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>91</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>46</v>
+      </c>
+      <c r="E16">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>83</v>
+      </c>
+      <c r="H16">
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>24</v>
+      </c>
+      <c r="J16">
+        <v>76</v>
+      </c>
+      <c r="L16">
+        <v>81</v>
+      </c>
+      <c r="M16">
+        <v>19</v>
+      </c>
+      <c r="N16">
+        <v>21</v>
+      </c>
+      <c r="O16">
+        <v>79</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>27.5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="7"/>
+        <v>20.5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="9"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="11"/>
+        <v>2.6666666666666679</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>80</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>26</v>
+      </c>
+      <c r="E26">
+        <v>74</v>
+      </c>
+      <c r="G26">
+        <v>82</v>
+      </c>
+      <c r="H26">
+        <v>18</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <v>90</v>
+      </c>
+      <c r="L26">
+        <v>70</v>
+      </c>
+      <c r="M26">
+        <v>30</v>
+      </c>
+      <c r="N26">
+        <v>18</v>
+      </c>
+      <c r="O26">
+        <v>82</v>
+      </c>
+      <c r="Q26">
+        <f>AVERAGE(C26:D26)</f>
+        <v>23</v>
+      </c>
+      <c r="R26">
+        <f>AVERAGE(H26:I26)</f>
+        <v>14</v>
+      </c>
+      <c r="S26">
+        <f>AVERAGE(M26:N26)</f>
+        <v>24</v>
+      </c>
+      <c r="T26">
+        <f>AVERAGE(Q26:S26)</f>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U26">
+        <f>AVERAGE(Q26:Q37)</f>
+        <v>26.6</v>
+      </c>
+      <c r="V26">
+        <f>_xlfn.STDEV.S(Q26:Q37)</f>
+        <v>2.8809720581775866</v>
+      </c>
+      <c r="W26">
+        <f>AVERAGE(R26:R37)</f>
+        <v>17.2</v>
+      </c>
+      <c r="X26">
+        <f>_xlfn.STDEV.S(R26:R37)</f>
+        <v>3.5106979363083899</v>
+      </c>
+      <c r="Y26">
+        <f>AVERAGE(S26:S37)</f>
+        <v>21.4</v>
+      </c>
+      <c r="Z26">
+        <f>_xlfn.STDEV.S(S26:S37)</f>
+        <v>2.6076809620810506</v>
+      </c>
+      <c r="AA26">
+        <f>AVERAGE(T26:T37)</f>
+        <v>21.733333333333334</v>
+      </c>
+      <c r="AB26">
+        <f>_xlfn.STDEV.S(T26:T37)</f>
+        <v>1.2281422284627033</v>
+      </c>
+      <c r="AC26">
+        <f>MIN(Q26:S26)</f>
+        <v>14</v>
+      </c>
+      <c r="AD26">
+        <f>T26-AC26</f>
+        <v>6.3333333333333321</v>
+      </c>
+      <c r="AE26">
+        <f>AVERAGE(AD26:AD37)</f>
+        <v>4.8333333333333339</v>
+      </c>
+      <c r="AF26">
+        <f>_xlfn.STDEV.S(AD26:AD37)</f>
+        <v>2.4152294576982389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>90</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>48</v>
+      </c>
+      <c r="E27">
+        <v>52</v>
+      </c>
+      <c r="G27">
+        <v>86</v>
+      </c>
+      <c r="H27">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>19</v>
+      </c>
+      <c r="J27">
+        <v>81</v>
+      </c>
+      <c r="L27">
+        <v>85</v>
+      </c>
+      <c r="M27">
+        <v>15</v>
+      </c>
+      <c r="N27">
+        <v>25</v>
+      </c>
+      <c r="O27">
+        <v>75</v>
+      </c>
+      <c r="Q27">
+        <f>AVERAGE(C27:D27)</f>
+        <v>29</v>
+      </c>
+      <c r="R27">
+        <f>AVERAGE(H27:I27)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S27">
+        <f>AVERAGE(M27:N27)</f>
+        <v>20</v>
+      </c>
+      <c r="T27">
+        <f>AVERAGE(Q27:S27)</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AC27">
+        <f>MIN(Q27:S27)</f>
+        <v>16.5</v>
+      </c>
+      <c r="AD27">
+        <f>T27-AC27</f>
+        <v>5.3333333333333321</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>86</v>
+      </c>
+      <c r="C28">
+        <v>14</v>
+      </c>
+      <c r="D28">
+        <v>38</v>
+      </c>
+      <c r="E28">
+        <v>62</v>
+      </c>
+      <c r="G28">
+        <v>84</v>
+      </c>
+      <c r="H28">
+        <v>16</v>
+      </c>
+      <c r="I28">
+        <v>23</v>
+      </c>
+      <c r="J28">
+        <v>77</v>
+      </c>
+      <c r="L28">
+        <v>83</v>
+      </c>
+      <c r="M28">
+        <v>17</v>
+      </c>
+      <c r="N28">
+        <v>19</v>
+      </c>
+      <c r="O28">
+        <v>81</v>
+      </c>
+      <c r="Q28">
+        <f>AVERAGE(C28:D28)</f>
+        <v>26</v>
+      </c>
+      <c r="R28">
+        <f>AVERAGE(H28:I28)</f>
+        <v>19.5</v>
+      </c>
+      <c r="S28">
+        <f>AVERAGE(M28:N28)</f>
+        <v>18</v>
+      </c>
+      <c r="T28">
+        <f>AVERAGE(Q28:S28)</f>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="AC28">
+        <f>MIN(Q28:S28)</f>
+        <v>18</v>
+      </c>
+      <c r="AD28">
+        <f>T28-AC28</f>
+        <v>3.1666666666666679</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>94</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>54</v>
+      </c>
+      <c r="E29">
+        <v>46</v>
+      </c>
+      <c r="G29">
+        <v>91</v>
+      </c>
+      <c r="H29">
+        <v>9</v>
+      </c>
+      <c r="I29">
+        <v>19</v>
+      </c>
+      <c r="J29">
+        <v>81</v>
+      </c>
+      <c r="L29">
+        <v>79</v>
+      </c>
+      <c r="M29">
+        <v>21</v>
+      </c>
+      <c r="N29">
+        <v>21</v>
+      </c>
+      <c r="O29">
+        <v>79</v>
+      </c>
+      <c r="Q29">
+        <f>AVERAGE(C29:D29)</f>
+        <v>30</v>
+      </c>
+      <c r="R29">
+        <f>AVERAGE(H29:I29)</f>
+        <v>14</v>
+      </c>
+      <c r="S29">
+        <f>AVERAGE(M29:N29)</f>
+        <v>21</v>
+      </c>
+      <c r="T29">
+        <f>AVERAGE(Q29:S29)</f>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC29">
+        <f>MIN(Q29:S29)</f>
+        <v>14</v>
+      </c>
+      <c r="AD29">
+        <f>T29-AC29</f>
+        <v>7.6666666666666679</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>95</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30">
+        <v>45</v>
+      </c>
+      <c r="E30">
+        <v>55</v>
+      </c>
+      <c r="G30">
+        <v>77</v>
+      </c>
+      <c r="H30">
+        <v>23</v>
+      </c>
+      <c r="I30">
+        <v>21</v>
+      </c>
+      <c r="J30">
+        <v>79</v>
+      </c>
+      <c r="L30">
+        <v>78</v>
+      </c>
+      <c r="M30">
+        <v>22</v>
+      </c>
+      <c r="N30">
+        <v>26</v>
+      </c>
+      <c r="O30">
+        <v>74</v>
+      </c>
+      <c r="Q30">
+        <f>AVERAGE(C30:D30)</f>
+        <v>25</v>
+      </c>
+      <c r="R30">
+        <f>AVERAGE(H30:I30)</f>
+        <v>22</v>
+      </c>
+      <c r="S30">
+        <f>AVERAGE(M30:N30)</f>
+        <v>24</v>
+      </c>
+      <c r="T30">
+        <f>AVERAGE(Q30:S30)</f>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="AC30">
+        <f>MIN(Q30:S30)</f>
+        <v>22</v>
+      </c>
+      <c r="AD30">
+        <f>T30-AC30</f>
+        <v>1.6666666666666679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12194,7 +13930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12618,7 +14354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13102,555 +14838,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
-  <dimension ref="A2:AF10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" t="s">
-        <v>55</v>
-      </c>
-      <c r="X2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>90</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>36</v>
-      </c>
-      <c r="E4">
-        <v>64</v>
-      </c>
-      <c r="G4">
-        <v>74</v>
-      </c>
-      <c r="H4">
-        <v>26</v>
-      </c>
-      <c r="I4">
-        <v>13</v>
-      </c>
-      <c r="J4">
-        <v>87</v>
-      </c>
-      <c r="L4">
-        <v>80</v>
-      </c>
-      <c r="M4">
-        <v>20</v>
-      </c>
-      <c r="N4">
-        <v>24</v>
-      </c>
-      <c r="O4">
-        <v>76</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>23</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>19.5</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>22</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>21.5</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q10)</f>
-        <v>22.571428571428573</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q10)</f>
-        <v>2.2808728487973529</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R10)</f>
-        <v>20.714285714285715</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R10)</f>
-        <v>1.8224786888818676</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S10)</f>
-        <v>25.071428571428573</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S10)</f>
-        <v>3.2071349029490825</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T10)</f>
-        <v>22.785714285714288</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T10)</f>
-        <v>1.2572540835836763</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>19.5</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>2</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD10)</f>
-        <v>2.6428571428571432</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD10)</f>
-        <v>1.8669359216239139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>89</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>29</v>
-      </c>
-      <c r="E5">
-        <v>71</v>
-      </c>
-      <c r="G5">
-        <v>62</v>
-      </c>
-      <c r="H5">
-        <v>38</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>91</v>
-      </c>
-      <c r="L5">
-        <v>69</v>
-      </c>
-      <c r="M5">
-        <v>31</v>
-      </c>
-      <c r="N5">
-        <v>24</v>
-      </c>
-      <c r="O5">
-        <v>76</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
-        <v>20</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
-        <v>23.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
-        <v>27.5</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
-        <v>23.666666666666668</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC10" si="4">MIN(Q5:S5)</f>
-        <v>20</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD10" si="5">T5-AC5</f>
-        <v>3.6666666666666679</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>89</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>31</v>
-      </c>
-      <c r="E6">
-        <v>69</v>
-      </c>
-      <c r="G6">
-        <v>74</v>
-      </c>
-      <c r="H6">
-        <v>26</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>87</v>
-      </c>
-      <c r="L6">
-        <v>76</v>
-      </c>
-      <c r="M6">
-        <v>24</v>
-      </c>
-      <c r="N6">
-        <v>22</v>
-      </c>
-      <c r="O6">
-        <v>78</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>19.5</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>21.166666666666668</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>19.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>1.6666666666666679</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>92</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>67</v>
-      </c>
-      <c r="G7">
-        <v>74</v>
-      </c>
-      <c r="H7">
-        <v>26</v>
-      </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>86</v>
-      </c>
-      <c r="L7">
-        <v>71</v>
-      </c>
-      <c r="M7">
-        <v>29</v>
-      </c>
-      <c r="N7">
-        <v>26</v>
-      </c>
-      <c r="O7">
-        <v>74</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>20.5</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>27.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>22.666666666666668</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>2.6666666666666679</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>94</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>44</v>
-      </c>
-      <c r="E8">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>71</v>
-      </c>
-      <c r="H8">
-        <v>29</v>
-      </c>
-      <c r="I8">
-        <v>16</v>
-      </c>
-      <c r="J8">
-        <v>84</v>
-      </c>
-      <c r="L8">
-        <v>81</v>
-      </c>
-      <c r="M8">
-        <v>19</v>
-      </c>
-      <c r="N8">
-        <v>25</v>
-      </c>
-      <c r="O8">
-        <v>75</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>22.5</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>23.166666666666668</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>1.1666666666666679</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>90</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>58</v>
-      </c>
-      <c r="G9">
-        <v>79</v>
-      </c>
-      <c r="H9">
-        <v>21</v>
-      </c>
-      <c r="I9">
-        <v>16</v>
-      </c>
-      <c r="J9">
-        <v>84</v>
-      </c>
-      <c r="L9">
-        <v>78</v>
-      </c>
-      <c r="M9">
-        <v>22</v>
-      </c>
-      <c r="N9">
-        <v>38</v>
-      </c>
-      <c r="O9">
-        <v>62</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>18.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>24.833333333333332</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>18.5</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>6.3333333333333321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>87</v>
-      </c>
-      <c r="C10">
-        <v>13</v>
-      </c>
-      <c r="D10">
-        <v>32</v>
-      </c>
-      <c r="E10">
-        <v>68</v>
-      </c>
-      <c r="G10">
-        <v>70</v>
-      </c>
-      <c r="H10">
-        <v>30</v>
-      </c>
-      <c r="I10">
-        <v>13</v>
-      </c>
-      <c r="J10">
-        <v>87</v>
-      </c>
-      <c r="L10">
-        <v>70</v>
-      </c>
-      <c r="M10">
-        <v>30</v>
-      </c>
-      <c r="N10">
-        <v>17</v>
-      </c>
-      <c r="O10">
-        <v>83</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="1"/>
-        <v>21.5</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="2"/>
-        <v>23.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="3"/>
-        <v>22.5</v>
-      </c>
-      <c r="AC10">
-        <f t="shared" si="4"/>
-        <v>21.5</v>
-      </c>
-      <c r="AD10">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DataAnalysis/CS/0.05/Results.xlsx
+++ b/DataAnalysis/CS/0.05/Results.xlsx
@@ -8,29 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CS\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF60B16-DC22-4492-A2B5-E22ED204F6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E408217E-6D8C-4659-A73F-218DB63562D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId4"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId8"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId9"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId11"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
+    <sheet name="DIFF_ONLYMIN" sheetId="21" r:id="rId2"/>
+    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId3"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId4"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId5"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId6"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId7"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId8"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId9"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId10"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId11"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId12"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId13"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId14"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId16"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId17"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId18"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="73">
   <si>
     <t>Dati originali</t>
   </si>
@@ -589,13 +590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -630,12 +631,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>4</v>
       </c>
@@ -670,7 +671,7 @@
         <v>2.3094010767585034</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
@@ -708,12 +709,12 @@
         <v>1.1666666666666661</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>51</v>
       </c>
@@ -751,7 +752,7 @@
         <v>2.8394541729001377</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>52</v>
       </c>
@@ -789,7 +790,7 @@
         <v>1.6576143053150778</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>50</v>
       </c>
@@ -824,7 +825,7 @@
         <v>1.4992281965015155</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>72</v>
       </c>
@@ -853,516 +854,584 @@
         <v>2.1235016504018209</v>
       </c>
       <c r="O9">
-        <v>3.0555555555555549</v>
+        <v>3.05555555555555</v>
       </c>
       <c r="P9">
         <v>2.0161385901804505</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+      <c r="R9">
+        <v>23</v>
+      </c>
+      <c r="S9">
+        <v>2.857738033247041</v>
+      </c>
+      <c r="T9">
+        <v>17.75</v>
+      </c>
+      <c r="U9">
+        <v>2.6614532371118851</v>
+      </c>
+      <c r="V9">
+        <v>23.625</v>
+      </c>
+      <c r="W9">
+        <v>2.4281337140555777</v>
+      </c>
+      <c r="X9">
+        <v>21.458333333333332</v>
+      </c>
+      <c r="Y9">
+        <v>1.9069803549260991</v>
+      </c>
+      <c r="Z9">
+        <v>3.708333333333333</v>
+      </c>
+      <c r="AA9">
+        <v>2.3858184402065521</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10">
+        <v>23</v>
+      </c>
+      <c r="H10">
+        <v>2.857738033247041</v>
+      </c>
+      <c r="I10">
+        <v>17.75</v>
+      </c>
+      <c r="J10">
+        <v>2.6614532371118851</v>
+      </c>
+      <c r="K10">
+        <v>23.625</v>
+      </c>
+      <c r="L10">
+        <v>2.4281337140555777</v>
+      </c>
+      <c r="M10">
+        <v>21.458333333333332</v>
+      </c>
+      <c r="N10">
+        <v>1.9069803549260991</v>
+      </c>
+      <c r="O10">
+        <v>3.708333333333333</v>
+      </c>
+      <c r="P10">
+        <v>2.3858184402065521</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
         <v>4</v>
       </c>
-      <c r="G11">
+      <c r="G13">
         <v>23.45</v>
       </c>
-      <c r="H11">
+      <c r="H13">
         <v>2.6399705385561569</v>
       </c>
-      <c r="I11">
+      <c r="I13">
         <v>20.2</v>
       </c>
-      <c r="J11">
+      <c r="J13">
         <v>2.8205594401741556</v>
       </c>
-      <c r="K11">
+      <c r="K13">
         <v>25.95</v>
       </c>
-      <c r="L11">
+      <c r="L13">
         <v>1.6236105170610073</v>
       </c>
-      <c r="M11">
+      <c r="M13">
         <v>23.2</v>
       </c>
-      <c r="N11">
+      <c r="N13">
         <v>1.6059303676308667</v>
       </c>
-      <c r="O11">
+      <c r="O13">
         <v>3.0999999999999996</v>
       </c>
-      <c r="P11">
+      <c r="P13">
         <v>1.8260799273949007</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
         <v>2</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F14" t="s">
         <v>21</v>
       </c>
-      <c r="G12">
+      <c r="G14">
         <v>23.625</v>
       </c>
-      <c r="H12">
+      <c r="H14">
         <v>3.0325613879076827</v>
       </c>
-      <c r="I12">
+      <c r="I14">
         <v>19.75</v>
       </c>
-      <c r="J12">
+      <c r="J14">
         <v>3.1847852585154217</v>
       </c>
-      <c r="K12">
+      <c r="K14">
         <v>21.9375</v>
       </c>
-      <c r="L12">
+      <c r="L14">
         <v>1.9353386562267894</v>
       </c>
-      <c r="M12">
+      <c r="M14">
         <v>21.770833333333332</v>
       </c>
-      <c r="N12">
+      <c r="N14">
         <v>1.1301689015504479</v>
       </c>
-      <c r="O12">
+      <c r="O14">
         <v>2.7708333333333339</v>
       </c>
-      <c r="P12">
+      <c r="P14">
         <v>1.4932055111111457</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15">
-        <v>22.571428571428573</v>
-      </c>
-      <c r="H15">
-        <v>2.2808728487973529</v>
-      </c>
-      <c r="I15">
-        <v>20.714285714285715</v>
-      </c>
-      <c r="J15">
-        <v>1.8224786888818676</v>
-      </c>
-      <c r="K15">
-        <v>25.071428571428573</v>
-      </c>
-      <c r="L15">
-        <v>3.2071349029490825</v>
-      </c>
-      <c r="M15">
-        <v>22.785714285714288</v>
-      </c>
-      <c r="N15">
-        <v>1.2572540835836763</v>
-      </c>
-      <c r="O15">
-        <v>2.6428571428571432</v>
-      </c>
-      <c r="P15">
-        <v>1.8669359216239139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16">
-        <v>23.5</v>
-      </c>
-      <c r="H16">
-        <v>2.5495097567963922</v>
-      </c>
-      <c r="I16">
-        <v>19</v>
-      </c>
-      <c r="J16">
-        <v>4.0373258476372698</v>
-      </c>
-      <c r="K16">
-        <v>19.75</v>
-      </c>
-      <c r="L16">
-        <v>1.6046806535881213</v>
-      </c>
-      <c r="M16">
-        <v>20.750000000000004</v>
-      </c>
-      <c r="N16">
-        <v>1.7344547654330258</v>
-      </c>
-      <c r="O16">
-        <v>3.2500000000000004</v>
-      </c>
-      <c r="P16">
-        <v>1.6253204812179864</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>22.571428571428573</v>
+      </c>
+      <c r="H17">
+        <v>2.2808728487973529</v>
+      </c>
+      <c r="I17">
+        <v>20.714285714285715</v>
+      </c>
+      <c r="J17">
+        <v>1.8224786888818676</v>
+      </c>
+      <c r="K17">
+        <v>25.071428571428573</v>
+      </c>
+      <c r="L17">
+        <v>3.2071349029490825</v>
+      </c>
+      <c r="M17">
+        <v>22.785714285714288</v>
+      </c>
+      <c r="N17">
+        <v>1.2572540835836763</v>
+      </c>
+      <c r="O17">
+        <v>2.6428571428571432</v>
+      </c>
+      <c r="P17">
+        <v>1.8669359216239139</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>23.5</v>
+      </c>
+      <c r="H18">
+        <v>2.5495097567963922</v>
+      </c>
+      <c r="I18">
+        <v>19</v>
+      </c>
+      <c r="J18">
+        <v>4.0373258476372698</v>
+      </c>
+      <c r="K18">
+        <v>19.75</v>
+      </c>
+      <c r="L18">
+        <v>1.6046806535881213</v>
+      </c>
+      <c r="M18">
+        <v>20.750000000000004</v>
+      </c>
+      <c r="N18">
+        <v>1.7344547654330258</v>
+      </c>
+      <c r="O18">
+        <v>3.2500000000000004</v>
+      </c>
+      <c r="P18">
+        <v>1.6253204812179864</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>21.85</v>
-      </c>
-      <c r="H18">
-        <v>1.8112303982529545</v>
-      </c>
-      <c r="I18">
-        <v>19.3</v>
-      </c>
-      <c r="J18">
-        <v>2.3828088000882</v>
-      </c>
-      <c r="K18">
-        <v>21.3</v>
-      </c>
-      <c r="L18">
-        <v>3.2846444082866761</v>
-      </c>
-      <c r="M18">
-        <v>20.81666666666667</v>
-      </c>
-      <c r="N18">
-        <v>1.5425047771901135</v>
-      </c>
-      <c r="O18">
-        <v>2.4166666666666661</v>
-      </c>
-      <c r="P18">
-        <v>1.0191075737691182</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19">
-        <v>26.6</v>
-      </c>
-      <c r="H19">
-        <v>2.8809720581775866</v>
-      </c>
-      <c r="I19">
-        <v>17.2</v>
-      </c>
-      <c r="J19">
-        <v>3.5106979363083899</v>
-      </c>
-      <c r="K19">
-        <v>21.4</v>
-      </c>
-      <c r="L19">
-        <v>2.6076809620810506</v>
-      </c>
-      <c r="M19">
-        <v>21.733333333333334</v>
-      </c>
-      <c r="N19">
-        <v>1.2281422284627033</v>
-      </c>
-      <c r="O19">
-        <v>4.8333333333333339</v>
-      </c>
-      <c r="P19">
-        <v>2.4152294576982389</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="G20">
+        <v>21.85</v>
+      </c>
+      <c r="H20">
+        <v>1.8112303982529545</v>
+      </c>
+      <c r="I20">
+        <v>19.3</v>
+      </c>
+      <c r="J20">
+        <v>2.3828088000882</v>
+      </c>
+      <c r="K20">
+        <v>21.3</v>
+      </c>
+      <c r="L20">
+        <v>3.2846444082866761</v>
+      </c>
+      <c r="M20">
+        <v>20.81666666666667</v>
+      </c>
+      <c r="N20">
+        <v>1.5425047771901135</v>
+      </c>
+      <c r="O20">
+        <v>2.4166666666666661</v>
+      </c>
+      <c r="P20">
+        <v>1.0191075737691182</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21">
+        <v>26.6</v>
+      </c>
+      <c r="H21">
+        <v>2.8809720581775866</v>
+      </c>
+      <c r="I21">
+        <v>17.2</v>
+      </c>
+      <c r="J21">
+        <v>3.5106979363083899</v>
+      </c>
+      <c r="K21">
+        <v>21.4</v>
+      </c>
+      <c r="L21">
+        <v>2.6076809620810506</v>
+      </c>
+      <c r="M21">
+        <v>21.733333333333334</v>
+      </c>
+      <c r="N21">
+        <v>1.2281422284627033</v>
+      </c>
+      <c r="O21">
+        <v>4.8333333333333339</v>
+      </c>
+      <c r="P21">
+        <v>2.4152294576982389</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
         <v>66</v>
       </c>
-      <c r="G21">
+      <c r="G23">
         <v>23.75</v>
       </c>
-      <c r="H21">
+      <c r="H23">
         <v>3.5237290853109955</v>
       </c>
-      <c r="I21">
+      <c r="I23">
         <v>22.5</v>
       </c>
-      <c r="J21">
+      <c r="J23">
         <v>0.40824829046386302</v>
       </c>
-      <c r="K21">
+      <c r="K23">
         <v>21.75</v>
       </c>
-      <c r="L21">
+      <c r="L23">
         <v>3.662876829305985</v>
       </c>
-      <c r="M21">
+      <c r="M23">
         <v>22.666666666666664</v>
       </c>
-      <c r="N21">
+      <c r="N23">
         <v>2.3053882134718262</v>
       </c>
-      <c r="O21">
+      <c r="O23">
         <v>1.9166666666666661</v>
       </c>
-      <c r="P21">
+      <c r="P23">
         <v>0.67357531405456328</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E22" t="s">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
         <v>72</v>
       </c>
-      <c r="G22">
+      <c r="G24">
         <v>25.625</v>
       </c>
-      <c r="H22">
+      <c r="H24">
         <v>3.3260336739125176</v>
       </c>
-      <c r="I22">
+      <c r="I24">
         <v>19.125</v>
       </c>
-      <c r="J22">
+      <c r="J24">
         <v>0.62915286960589578</v>
       </c>
-      <c r="K22">
+      <c r="K24">
         <v>17.875</v>
       </c>
-      <c r="L22">
+      <c r="L24">
         <v>3.0923292192132452</v>
       </c>
-      <c r="M22">
+      <c r="M24">
         <v>20.875</v>
       </c>
-      <c r="N22">
+      <c r="N24">
         <v>1.3289859682117418</v>
       </c>
-      <c r="O22">
+      <c r="O24">
         <v>3.625</v>
       </c>
-      <c r="P22">
+      <c r="P24">
         <v>1.5949863577728434</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>19.333333333333332</v>
-      </c>
-      <c r="H25">
-        <v>2.2730302828309825</v>
-      </c>
-      <c r="I25">
-        <v>16.083333333333332</v>
-      </c>
-      <c r="J25">
-        <v>2.5964719653149833</v>
-      </c>
-      <c r="K25">
-        <v>24.083333333333332</v>
-      </c>
-      <c r="L25">
-        <v>1.9343388189938875</v>
-      </c>
-      <c r="M25">
-        <v>19.833333333333332</v>
-      </c>
-      <c r="N25">
-        <v>1.4220486005134358</v>
-      </c>
-      <c r="O25">
-        <v>3.75</v>
-      </c>
-      <c r="P25">
-        <v>2.0076243561870726</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26">
-        <v>21.3</v>
-      </c>
-      <c r="H26">
-        <v>1.6807736313971611</v>
-      </c>
-      <c r="I26">
-        <v>17.7</v>
-      </c>
-      <c r="J26">
-        <v>4.2514703338962612</v>
-      </c>
-      <c r="K26">
-        <v>21.8</v>
-      </c>
-      <c r="L26">
-        <v>1.2041594578792296</v>
-      </c>
-      <c r="M26">
-        <v>20.266666666666666</v>
-      </c>
-      <c r="N26">
-        <v>1.9811612756158954</v>
-      </c>
-      <c r="O26">
-        <v>2.8666666666666663</v>
-      </c>
-      <c r="P26">
-        <v>2.0186629238186353</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>19.333333333333332</v>
+      </c>
+      <c r="H27">
+        <v>2.2730302828309825</v>
+      </c>
+      <c r="I27">
+        <v>16.083333333333332</v>
+      </c>
+      <c r="J27">
+        <v>2.5964719653149833</v>
+      </c>
+      <c r="K27">
+        <v>24.083333333333332</v>
+      </c>
+      <c r="L27">
+        <v>1.9343388189938875</v>
+      </c>
+      <c r="M27">
+        <v>19.833333333333332</v>
+      </c>
+      <c r="N27">
+        <v>1.4220486005134358</v>
+      </c>
+      <c r="O27">
+        <v>3.75</v>
+      </c>
+      <c r="P27">
+        <v>2.0076243561870726</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>21.3</v>
+      </c>
+      <c r="H28">
+        <v>1.6807736313971611</v>
+      </c>
+      <c r="I28">
+        <v>17.7</v>
+      </c>
+      <c r="J28">
+        <v>4.2514703338962612</v>
+      </c>
+      <c r="K28">
+        <v>21.8</v>
+      </c>
+      <c r="L28">
+        <v>1.2041594578792296</v>
+      </c>
+      <c r="M28">
+        <v>20.266666666666666</v>
+      </c>
+      <c r="N28">
+        <v>1.9811612756158954</v>
+      </c>
+      <c r="O28">
+        <v>2.8666666666666663</v>
+      </c>
+      <c r="P28">
+        <v>2.0186629238186353</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
         <v>66</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E30" t="s">
         <v>72</v>
       </c>
-      <c r="G28">
+      <c r="G30">
         <v>23</v>
       </c>
-      <c r="H28">
+      <c r="H30">
         <v>0.70710678118654757</v>
       </c>
-      <c r="I28">
+      <c r="I30">
         <v>13.25</v>
       </c>
-      <c r="J28">
+      <c r="J30">
         <v>2.4748737341529163</v>
       </c>
-      <c r="K28">
+      <c r="K30">
         <v>22.75</v>
       </c>
-      <c r="L28">
+      <c r="L30">
         <v>2.4748737341529163</v>
       </c>
-      <c r="M28">
+      <c r="M30">
         <v>19.666666666666664</v>
       </c>
-      <c r="N28">
+      <c r="N30">
         <v>0.23570226039551501</v>
       </c>
-      <c r="O28">
+      <c r="O30">
         <v>6.4166666666666661</v>
       </c>
-      <c r="P28">
+      <c r="P30">
         <v>2.7105759945484333</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D29" t="s">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E30" t="s">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
         <v>66</v>
       </c>
-      <c r="G30">
+      <c r="G32">
         <v>23.833333333333332</v>
       </c>
-      <c r="H30">
+      <c r="H32">
         <v>1.0408329997330663</v>
       </c>
-      <c r="I30">
+      <c r="I32">
         <v>20</v>
       </c>
-      <c r="J30">
+      <c r="J32">
         <v>4.5</v>
       </c>
-      <c r="K30">
+      <c r="K32">
         <v>23.5</v>
       </c>
-      <c r="L30">
+      <c r="L32">
         <v>1.3228756555322954</v>
       </c>
-      <c r="M30">
+      <c r="M32">
         <v>22.444444444444446</v>
       </c>
-      <c r="N30">
+      <c r="N32">
         <v>1.4369463507086175</v>
       </c>
-      <c r="O30">
+      <c r="O32">
         <v>3.111111111111112</v>
       </c>
-      <c r="P30">
+      <c r="P32">
         <v>2.2381374531648541</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E31" t="s">
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
         <v>72</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>22.75</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <v>1.7677669529663689</v>
       </c>
-      <c r="I31">
+      <c r="I33">
         <v>19.5</v>
       </c>
-      <c r="J31">
+      <c r="J33">
         <v>0</v>
       </c>
-      <c r="K31">
+      <c r="K33">
         <v>21.5</v>
       </c>
-      <c r="L31">
+      <c r="L33">
         <v>6.3639610306789276</v>
       </c>
-      <c r="M31">
+      <c r="M33">
         <v>21.25</v>
       </c>
-      <c r="N31">
+      <c r="N33">
         <v>1.5320646925708512</v>
       </c>
-      <c r="O31">
+      <c r="O33">
         <v>3</v>
       </c>
-      <c r="P31">
+      <c r="P33">
         <v>0.2357022603955175</v>
       </c>
     </row>
@@ -1373,6 +1442,492 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
+  <dimension ref="A2:AF9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>88</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>68</v>
+      </c>
+      <c r="G4">
+        <v>77</v>
+      </c>
+      <c r="H4">
+        <v>23</v>
+      </c>
+      <c r="I4">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>87</v>
+      </c>
+      <c r="L4">
+        <v>72</v>
+      </c>
+      <c r="M4">
+        <v>28</v>
+      </c>
+      <c r="N4">
+        <v>23</v>
+      </c>
+      <c r="O4">
+        <v>77</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>22</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>18</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>25.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q9)</f>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q9)</f>
+        <v>2.2730302828309825</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R9)</f>
+        <v>16.083333333333332</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R9)</f>
+        <v>2.5964719653149833</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S9)</f>
+        <v>24.083333333333332</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S9)</f>
+        <v>1.9343388189938875</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T9)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T9)</f>
+        <v>1.4220486005134358</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>18</v>
+      </c>
+      <c r="AD4">
+        <f>(T4-AC4)</f>
+        <v>3.8333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD9)</f>
+        <v>3.75</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD9)</f>
+        <v>2.0076243561870726</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>85</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>72</v>
+      </c>
+      <c r="G5">
+        <v>83</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>90</v>
+      </c>
+      <c r="L5">
+        <v>85</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>33</v>
+      </c>
+      <c r="O5">
+        <v>67</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
+        <v>21.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
+        <v>13.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
+        <v>24</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
+        <v>13.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD9" si="5">(T5-AC5)</f>
+        <v>6.1666666666666679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>89</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>71</v>
+      </c>
+      <c r="G6">
+        <v>80</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>82</v>
+      </c>
+      <c r="L6">
+        <v>81</v>
+      </c>
+      <c r="M6">
+        <v>19</v>
+      </c>
+      <c r="N6">
+        <v>25</v>
+      </c>
+      <c r="O6">
+        <v>75</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>1.3333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>79</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>83</v>
+      </c>
+      <c r="G7">
+        <v>70</v>
+      </c>
+      <c r="H7">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>95</v>
+      </c>
+      <c r="L7">
+        <v>68</v>
+      </c>
+      <c r="M7">
+        <v>32</v>
+      </c>
+      <c r="N7">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>81</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>25.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>17.5</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>3.1666666666666679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>86</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>80</v>
+      </c>
+      <c r="H8">
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>95</v>
+      </c>
+      <c r="L8">
+        <v>69</v>
+      </c>
+      <c r="M8">
+        <v>31</v>
+      </c>
+      <c r="N8">
+        <v>21</v>
+      </c>
+      <c r="O8">
+        <v>79</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>18.5</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>88</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>79</v>
+      </c>
+      <c r="G9">
+        <v>76</v>
+      </c>
+      <c r="H9">
+        <v>24</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>92</v>
+      </c>
+      <c r="L9">
+        <v>77</v>
+      </c>
+      <c r="M9">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>20</v>
+      </c>
+      <c r="O9">
+        <v>80</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>21.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
   <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1923,7 +2478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2409,7 +2964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AN99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5112,7 +5667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5844,7 +6399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6437,7 +6992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AR14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7376,7 +7931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AR14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8315,7 +8870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10691,7 +11246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10990,6 +11545,354 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D05332-554B-48D6-B8B1-1EA56C11B3D2}">
+  <dimension ref="B1:AF5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>86</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+      <c r="G2">
+        <v>84</v>
+      </c>
+      <c r="H2">
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <v>13</v>
+      </c>
+      <c r="J2">
+        <v>87</v>
+      </c>
+      <c r="L2">
+        <v>76</v>
+      </c>
+      <c r="M2">
+        <v>24</v>
+      </c>
+      <c r="N2">
+        <v>26</v>
+      </c>
+      <c r="O2">
+        <v>74</v>
+      </c>
+      <c r="Q2">
+        <f>AVERAGE(C2,D2)</f>
+        <v>24.5</v>
+      </c>
+      <c r="R2">
+        <f>AVERAGE(H2,I2)</f>
+        <v>14.5</v>
+      </c>
+      <c r="S2">
+        <f>AVERAGE(M2,N2)</f>
+        <v>25</v>
+      </c>
+      <c r="T2">
+        <f t="shared" ref="T2" si="0">AVERAGE(Q2:S2)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U2">
+        <f>AVERAGE(Q2:Q5)</f>
+        <v>23</v>
+      </c>
+      <c r="V2">
+        <f>_xlfn.STDEV.S(Q2:Q5)</f>
+        <v>2.857738033247041</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGE(R2:R6)</f>
+        <v>17.75</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.STDEV.S(R2:R5)</f>
+        <v>2.6614532371118851</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGE(S2:S5)</f>
+        <v>23.625</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.STDEV.S(S2:S5)</f>
+        <v>2.4281337140555777</v>
+      </c>
+      <c r="AA2">
+        <f>AVERAGE(T2:T5)</f>
+        <v>21.458333333333332</v>
+      </c>
+      <c r="AB2">
+        <f>_xlfn.STDEV.S(T2:T5)</f>
+        <v>1.9069803549260991</v>
+      </c>
+      <c r="AC2">
+        <f>MIN(Q2:S2)</f>
+        <v>14.5</v>
+      </c>
+      <c r="AD2">
+        <f>T2-AC2</f>
+        <v>6.8333333333333321</v>
+      </c>
+      <c r="AE2">
+        <f>AVERAGE(AD2:AD5)</f>
+        <v>3.708333333333333</v>
+      </c>
+      <c r="AF2">
+        <f>_xlfn.STDEV.S(AD2:AD5)</f>
+        <v>2.3858184402065521</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>89</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>72</v>
+      </c>
+      <c r="G3">
+        <v>73</v>
+      </c>
+      <c r="H3">
+        <v>27</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>91</v>
+      </c>
+      <c r="L3">
+        <v>79</v>
+      </c>
+      <c r="M3">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>81</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q5" si="1">AVERAGE(C3,D3)</f>
+        <v>19.5</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R5" si="2">AVERAGE(H3,I3)</f>
+        <v>18</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S5" si="3">AVERAGE(M3,N3)</f>
+        <v>20</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T5" si="4">AVERAGE(Q3:S3)</f>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" ref="AC3:AC5" si="5">MIN(Q3:S3)</f>
+        <v>18</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" ref="AD3:AD5" si="6">T3-AC3</f>
+        <v>1.1666666666666679</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>91</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>43</v>
+      </c>
+      <c r="E4">
+        <v>57</v>
+      </c>
+      <c r="G4">
+        <v>85</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>73</v>
+      </c>
+      <c r="L4">
+        <v>74</v>
+      </c>
+      <c r="M4">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <v>23</v>
+      </c>
+      <c r="O4">
+        <v>77</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="3"/>
+        <v>24.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="6"/>
+        <v>2.8333333333333321</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>91</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>35</v>
+      </c>
+      <c r="E5">
+        <v>65</v>
+      </c>
+      <c r="G5">
+        <v>81</v>
+      </c>
+      <c r="H5">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>84</v>
+      </c>
+      <c r="L5">
+        <v>72</v>
+      </c>
+      <c r="M5">
+        <v>28</v>
+      </c>
+      <c r="N5">
+        <v>22</v>
+      </c>
+      <c r="O5">
+        <v>78</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="2"/>
+        <v>17.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>21.5</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="5"/>
+        <v>17.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F502F8F-7F4F-4035-A5E9-9B448496FCE0}">
   <dimension ref="B1:AF3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11213,7 +12116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
   <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11616,19 +12519,19 @@
         <v>81</v>
       </c>
       <c r="Q10">
-        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C10,D10)</f>
+        <f t="shared" ref="Q10:Q13" si="6">AVERAGE(C10,D10)</f>
         <v>23.5</v>
       </c>
       <c r="R10">
-        <f t="shared" ref="R8:R13" si="7">AVERAGE(H10,I10)</f>
+        <f t="shared" ref="R10:R13" si="7">AVERAGE(H10,I10)</f>
         <v>19</v>
       </c>
       <c r="S10">
-        <f t="shared" ref="S8:S13" si="8">AVERAGE(M10,N10)</f>
+        <f t="shared" ref="S10:S13" si="8">AVERAGE(M10,N10)</f>
         <v>21.5</v>
       </c>
       <c r="T10">
-        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q10:S10)</f>
+        <f t="shared" ref="T10:T13" si="9">AVERAGE(Q10:S10)</f>
         <v>21.333333333333332</v>
       </c>
       <c r="U10">
@@ -11664,11 +12567,11 @@
         <v>1.3289859682117418</v>
       </c>
       <c r="AC10">
-        <f t="shared" ref="AC8:AC13" si="10">MIN(Q10:S10)</f>
+        <f t="shared" ref="AC10:AC13" si="10">MIN(Q10:S10)</f>
         <v>19</v>
       </c>
       <c r="AD10">
-        <f t="shared" ref="AD8:AD13" si="11">T10-AC10</f>
+        <f t="shared" ref="AD10:AD13" si="11">T10-AC10</f>
         <v>2.3333333333333321</v>
       </c>
       <c r="AE10">
@@ -11871,7 +12774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12037,7 +12940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
   <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12380,19 +13283,19 @@
         <v>78</v>
       </c>
       <c r="Q10">
-        <f t="shared" ref="Q7:Q11" si="6">AVERAGE(C10:D10)</f>
+        <f t="shared" ref="Q10:Q11" si="6">AVERAGE(C10:D10)</f>
         <v>24</v>
       </c>
       <c r="R10">
-        <f t="shared" ref="R7:R11" si="7">AVERAGE(H10:I10)</f>
+        <f t="shared" ref="R10:R11" si="7">AVERAGE(H10:I10)</f>
         <v>19.5</v>
       </c>
       <c r="S10">
-        <f t="shared" ref="S7:S11" si="8">AVERAGE(M10:N10)</f>
+        <f t="shared" ref="S10:S11" si="8">AVERAGE(M10:N10)</f>
         <v>17</v>
       </c>
       <c r="T10">
-        <f t="shared" ref="T7:T11" si="9">AVERAGE(Q10:S10)</f>
+        <f t="shared" ref="T10:T11" si="9">AVERAGE(Q10:S10)</f>
         <v>20.166666666666668</v>
       </c>
       <c r="U10">
@@ -12428,11 +13331,11 @@
         <v>1.5320646925708512</v>
       </c>
       <c r="AC10">
-        <f t="shared" ref="AC7:AC11" si="10">MIN(Q10:S10)</f>
+        <f t="shared" ref="AC10:AC11" si="10">MIN(Q10:S10)</f>
         <v>17</v>
       </c>
       <c r="AD10">
-        <f t="shared" ref="AD7:AD11" si="11">T10-AC10</f>
+        <f t="shared" ref="AD10:AD11" si="11">T10-AC10</f>
         <v>3.1666666666666679</v>
       </c>
       <c r="AE10">
@@ -12511,7 +13414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
   <dimension ref="A2:AF30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13767,7 +14670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13930,7 +14833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14352,490 +15255,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
-  <dimension ref="A2:AF9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" t="s">
-        <v>55</v>
-      </c>
-      <c r="X2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>88</v>
-      </c>
-      <c r="C4">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>32</v>
-      </c>
-      <c r="E4">
-        <v>68</v>
-      </c>
-      <c r="G4">
-        <v>77</v>
-      </c>
-      <c r="H4">
-        <v>23</v>
-      </c>
-      <c r="I4">
-        <v>13</v>
-      </c>
-      <c r="J4">
-        <v>87</v>
-      </c>
-      <c r="L4">
-        <v>72</v>
-      </c>
-      <c r="M4">
-        <v>28</v>
-      </c>
-      <c r="N4">
-        <v>23</v>
-      </c>
-      <c r="O4">
-        <v>77</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>22</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>18</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>25.5</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>21.833333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q9)</f>
-        <v>19.333333333333332</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q9)</f>
-        <v>2.2730302828309825</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R9)</f>
-        <v>16.083333333333332</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R9)</f>
-        <v>2.5964719653149833</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S9)</f>
-        <v>24.083333333333332</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S9)</f>
-        <v>1.9343388189938875</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T9)</f>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T9)</f>
-        <v>1.4220486005134358</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>18</v>
-      </c>
-      <c r="AD4">
-        <f>(T4-AC4)</f>
-        <v>3.8333333333333321</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD9)</f>
-        <v>3.75</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD9)</f>
-        <v>2.0076243561870726</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>85</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>72</v>
-      </c>
-      <c r="G5">
-        <v>83</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>90</v>
-      </c>
-      <c r="L5">
-        <v>85</v>
-      </c>
-      <c r="M5">
-        <v>15</v>
-      </c>
-      <c r="N5">
-        <v>33</v>
-      </c>
-      <c r="O5">
-        <v>67</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
-        <v>21.5</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
-        <v>13.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
-        <v>24</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
-        <v>19.666666666666668</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
-        <v>13.5</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD9" si="5">(T5-AC5)</f>
-        <v>6.1666666666666679</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>89</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>71</v>
-      </c>
-      <c r="G6">
-        <v>80</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <v>82</v>
-      </c>
-      <c r="L6">
-        <v>81</v>
-      </c>
-      <c r="M6">
-        <v>19</v>
-      </c>
-      <c r="N6">
-        <v>25</v>
-      </c>
-      <c r="O6">
-        <v>75</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>19</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>1.3333333333333321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>79</v>
-      </c>
-      <c r="C7">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>83</v>
-      </c>
-      <c r="G7">
-        <v>70</v>
-      </c>
-      <c r="H7">
-        <v>30</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>95</v>
-      </c>
-      <c r="L7">
-        <v>68</v>
-      </c>
-      <c r="M7">
-        <v>32</v>
-      </c>
-      <c r="N7">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>81</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>17.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>25.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>20.666666666666668</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>17.5</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>3.1666666666666679</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>86</v>
-      </c>
-      <c r="C8">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-      <c r="G8">
-        <v>80</v>
-      </c>
-      <c r="H8">
-        <v>20</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>95</v>
-      </c>
-      <c r="L8">
-        <v>69</v>
-      </c>
-      <c r="M8">
-        <v>31</v>
-      </c>
-      <c r="N8">
-        <v>21</v>
-      </c>
-      <c r="O8">
-        <v>79</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>12.5</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>26</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>18.5</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>12.5</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>88</v>
-      </c>
-      <c r="C9">
-        <v>12</v>
-      </c>
-      <c r="D9">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>79</v>
-      </c>
-      <c r="G9">
-        <v>76</v>
-      </c>
-      <c r="H9">
-        <v>24</v>
-      </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-      <c r="J9">
-        <v>92</v>
-      </c>
-      <c r="L9">
-        <v>77</v>
-      </c>
-      <c r="M9">
-        <v>23</v>
-      </c>
-      <c r="N9">
-        <v>20</v>
-      </c>
-      <c r="O9">
-        <v>80</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>21.5</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>